--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255055</v>
+        <v>121255024</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>57364</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613400</v>
+        <v>613541</v>
       </c>
       <c r="R2" t="n">
-        <v>7041781</v>
+        <v>7041685</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -749,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255052</v>
+        <v>121255055</v>
       </c>
       <c r="B3" t="n">
         <v>98071</v>
@@ -816,7 +817,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613542</v>
+        <v>613400</v>
       </c>
       <c r="R3" t="n">
-        <v>7041572</v>
+        <v>7041781</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -887,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121255024</v>
+        <v>121255052</v>
       </c>
       <c r="B4" t="n">
-        <v>57364</v>
+        <v>98071</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,31 +900,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613541</v>
+        <v>613542</v>
       </c>
       <c r="R4" t="n">
-        <v>7041685</v>
+        <v>7041572</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -962,12 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -4193,10 +4193,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121255058</v>
+        <v>121255037</v>
       </c>
       <c r="B36" t="n">
-        <v>91343</v>
+        <v>90652</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4205,25 +4205,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>898</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613546</v>
+        <v>613554</v>
       </c>
       <c r="R36" t="n">
-        <v>7041646</v>
+        <v>7041628</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4295,10 +4295,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121255037</v>
+        <v>121255058</v>
       </c>
       <c r="B37" t="n">
-        <v>90652</v>
+        <v>91343</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4307,25 +4307,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>898</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613554</v>
+        <v>613546</v>
       </c>
       <c r="R37" t="n">
-        <v>7041628</v>
+        <v>7041646</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255024</v>
+        <v>121255040</v>
       </c>
       <c r="B2" t="n">
-        <v>57364</v>
+        <v>90697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613541</v>
+        <v>613542</v>
       </c>
       <c r="R2" t="n">
-        <v>7041685</v>
+        <v>7041619</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -750,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255055</v>
+        <v>121255008</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>90662</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,42 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613400</v>
+        <v>613391</v>
       </c>
       <c r="R3" t="n">
-        <v>7041781</v>
+        <v>7041765</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -856,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121255052</v>
+        <v>121255050</v>
       </c>
       <c r="B4" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,42 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613542</v>
+        <v>613348</v>
       </c>
       <c r="R4" t="n">
-        <v>7041572</v>
+        <v>7041806</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -976,6 +963,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -994,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121255026</v>
+        <v>121255054</v>
       </c>
       <c r="B5" t="n">
-        <v>91127</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,34 +998,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613371</v>
+        <v>613568</v>
       </c>
       <c r="R5" t="n">
-        <v>7041736</v>
+        <v>7041618</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1049,7 +1041,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1059,17 +1051,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121255049</v>
+        <v>121255057</v>
       </c>
       <c r="B6" t="n">
-        <v>91127</v>
+        <v>90711</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,7 +1131,7 @@
         <v>613523</v>
       </c>
       <c r="R6" t="n">
-        <v>7041640</v>
+        <v>7041633</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1198,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121255013</v>
+        <v>121255014</v>
       </c>
       <c r="B7" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613465</v>
+        <v>613462</v>
       </c>
       <c r="R7" t="n">
-        <v>7041678</v>
+        <v>7041669</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1300,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121255041</v>
+        <v>121255009</v>
       </c>
       <c r="B8" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613536</v>
+        <v>613396</v>
       </c>
       <c r="R8" t="n">
-        <v>7041639</v>
+        <v>7041771</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1370,12 +1362,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121255015</v>
+        <v>121255019</v>
       </c>
       <c r="B9" t="n">
-        <v>90687</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1418,34 +1410,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613481</v>
+        <v>613528</v>
       </c>
       <c r="R9" t="n">
-        <v>7041676</v>
+        <v>7041701</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1478,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1504,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121255029</v>
+        <v>121255012</v>
       </c>
       <c r="B10" t="n">
-        <v>98071</v>
+        <v>90697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,42 +1518,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613510</v>
+        <v>613454</v>
       </c>
       <c r="R10" t="n">
-        <v>7041675</v>
+        <v>7041671</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1610,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121255056</v>
+        <v>121255058</v>
       </c>
       <c r="B11" t="n">
-        <v>98071</v>
+        <v>91353</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1626,38 +1624,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613391</v>
+        <v>613546</v>
       </c>
       <c r="R11" t="n">
-        <v>7041785</v>
+        <v>7041646</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1716,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121255045</v>
+        <v>121255021</v>
       </c>
       <c r="B12" t="n">
-        <v>56560</v>
+        <v>79711</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1756,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613481</v>
+        <v>613468</v>
       </c>
       <c r="R12" t="n">
-        <v>7041555</v>
+        <v>7041729</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1786,12 +1780,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1818,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121255040</v>
+        <v>121255023</v>
       </c>
       <c r="B13" t="n">
-        <v>90687</v>
+        <v>57367</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,34 +1828,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613542</v>
+        <v>613442</v>
       </c>
       <c r="R13" t="n">
-        <v>7041619</v>
+        <v>7041756</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1888,12 +1887,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1920,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121255021</v>
+        <v>121255037</v>
       </c>
       <c r="B14" t="n">
-        <v>79708</v>
+        <v>90662</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1960,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613468</v>
+        <v>613554</v>
       </c>
       <c r="R14" t="n">
-        <v>7041729</v>
+        <v>7041628</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1990,12 +1989,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2022,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121255051</v>
+        <v>121255006</v>
       </c>
       <c r="B15" t="n">
-        <v>79679</v>
+        <v>74708</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2038,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2062,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613451</v>
+        <v>613519</v>
       </c>
       <c r="R15" t="n">
-        <v>7041510</v>
+        <v>7041683</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2092,12 +2091,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2124,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121255025</v>
+        <v>121255026</v>
       </c>
       <c r="B16" t="n">
-        <v>91127</v>
+        <v>91137</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613463</v>
+        <v>613371</v>
       </c>
       <c r="R16" t="n">
-        <v>7041737</v>
+        <v>7041736</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2226,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121255011</v>
+        <v>121255016</v>
       </c>
       <c r="B17" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613415</v>
+        <v>613505</v>
       </c>
       <c r="R17" t="n">
-        <v>7041708</v>
+        <v>7041675</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2328,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121255023</v>
+        <v>121255013</v>
       </c>
       <c r="B18" t="n">
-        <v>57364</v>
+        <v>90697</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,39 +2343,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613442</v>
+        <v>613465</v>
       </c>
       <c r="R18" t="n">
-        <v>7041756</v>
+        <v>7041678</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2435,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121255008</v>
+        <v>121255045</v>
       </c>
       <c r="B19" t="n">
-        <v>90652</v>
+        <v>56563</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2451,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2475,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613391</v>
+        <v>613481</v>
       </c>
       <c r="R19" t="n">
-        <v>7041765</v>
+        <v>7041555</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2505,12 +2499,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2537,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121255032</v>
+        <v>121255025</v>
       </c>
       <c r="B20" t="n">
-        <v>78598</v>
+        <v>91137</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2549,25 +2543,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613446</v>
+        <v>613463</v>
       </c>
       <c r="R20" t="n">
-        <v>7041752</v>
+        <v>7041737</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2639,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121255057</v>
+        <v>121255056</v>
       </c>
       <c r="B21" t="n">
-        <v>90701</v>
+        <v>98081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2651,38 +2645,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613523</v>
+        <v>613391</v>
       </c>
       <c r="R21" t="n">
-        <v>7041633</v>
+        <v>7041785</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2741,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121255038</v>
+        <v>121255034</v>
       </c>
       <c r="B22" t="n">
-        <v>90652</v>
+        <v>78601</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2753,25 +2751,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2781,10 +2779,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613396</v>
+        <v>613618</v>
       </c>
       <c r="R22" t="n">
-        <v>7041694</v>
+        <v>7041721</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2796,7 +2794,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2806,17 +2804,17 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2843,10 +2841,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121255039</v>
+        <v>121255038</v>
       </c>
       <c r="B23" t="n">
-        <v>90652</v>
+        <v>90662</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2883,10 +2881,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613386</v>
+        <v>613396</v>
       </c>
       <c r="R23" t="n">
-        <v>7041700</v>
+        <v>7041694</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2945,10 +2943,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121255016</v>
+        <v>121255029</v>
       </c>
       <c r="B24" t="n">
-        <v>90687</v>
+        <v>98081</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2957,35 +2955,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613505</v>
+        <v>613510</v>
       </c>
       <c r="R24" t="n">
         <v>7041675</v>
@@ -3047,10 +3049,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121255031</v>
+        <v>121255055</v>
       </c>
       <c r="B25" t="n">
-        <v>90701</v>
+        <v>98081</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3059,38 +3061,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613377</v>
+        <v>613400</v>
       </c>
       <c r="R25" t="n">
-        <v>7041742</v>
+        <v>7041781</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3117,12 +3123,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3149,10 +3155,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121255042</v>
+        <v>121255044</v>
       </c>
       <c r="B26" t="n">
-        <v>90687</v>
+        <v>57351</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3165,34 +3171,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>613460</v>
+        <v>613475</v>
       </c>
       <c r="R26" t="n">
-        <v>7041672</v>
+        <v>7041662</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3225,6 +3236,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3251,10 +3267,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121255009</v>
+        <v>121255043</v>
       </c>
       <c r="B27" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3291,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>613396</v>
+        <v>613421</v>
       </c>
       <c r="R27" t="n">
-        <v>7041771</v>
+        <v>7041692</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3321,12 +3337,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3353,10 +3369,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121255006</v>
+        <v>121255010</v>
       </c>
       <c r="B28" t="n">
-        <v>74705</v>
+        <v>90697</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3369,21 +3385,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3393,10 +3409,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613519</v>
+        <v>613391</v>
       </c>
       <c r="R28" t="n">
-        <v>7041683</v>
+        <v>7041765</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3455,10 +3471,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121255053</v>
+        <v>121255042</v>
       </c>
       <c r="B29" t="n">
-        <v>98071</v>
+        <v>90697</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3467,42 +3483,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613554</v>
+        <v>613460</v>
       </c>
       <c r="R29" t="n">
-        <v>7041573</v>
+        <v>7041672</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3561,10 +3573,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121255044</v>
+        <v>121255015</v>
       </c>
       <c r="B30" t="n">
-        <v>57348</v>
+        <v>90697</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3577,39 +3589,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613475</v>
+        <v>613481</v>
       </c>
       <c r="R30" t="n">
-        <v>7041662</v>
+        <v>7041676</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3636,17 +3643,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3673,10 +3675,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121255048</v>
+        <v>121255051</v>
       </c>
       <c r="B31" t="n">
-        <v>57364</v>
+        <v>79682</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3689,39 +3691,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613373</v>
+        <v>613451</v>
       </c>
       <c r="R31" t="n">
-        <v>7041694</v>
+        <v>7041510</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3780,10 +3777,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121255050</v>
+        <v>121255011</v>
       </c>
       <c r="B32" t="n">
-        <v>79679</v>
+        <v>90697</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3796,21 +3793,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3820,10 +3817,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613348</v>
+        <v>613415</v>
       </c>
       <c r="R32" t="n">
-        <v>7041806</v>
+        <v>7041708</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3850,12 +3847,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3864,7 +3861,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3883,10 +3879,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121255014</v>
+        <v>121255041</v>
       </c>
       <c r="B33" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3923,10 +3919,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>613462</v>
+        <v>613536</v>
       </c>
       <c r="R33" t="n">
-        <v>7041669</v>
+        <v>7041639</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3953,12 +3949,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3985,10 +3981,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121255046</v>
+        <v>121255052</v>
       </c>
       <c r="B34" t="n">
-        <v>90707</v>
+        <v>98081</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3997,38 +3993,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>613534</v>
+        <v>613542</v>
       </c>
       <c r="R34" t="n">
-        <v>7041558</v>
+        <v>7041572</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4087,10 +4087,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121255054</v>
+        <v>121255048</v>
       </c>
       <c r="B35" t="n">
-        <v>98071</v>
+        <v>57367</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4099,30 +4099,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4131,10 +4132,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>613568</v>
+        <v>613373</v>
       </c>
       <c r="R35" t="n">
-        <v>7041618</v>
+        <v>7041694</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4146,7 +4147,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4156,7 +4157,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4193,10 +4194,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121255037</v>
+        <v>121255032</v>
       </c>
       <c r="B36" t="n">
-        <v>90652</v>
+        <v>78601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4205,25 +4206,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4233,10 +4234,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613554</v>
+        <v>613446</v>
       </c>
       <c r="R36" t="n">
-        <v>7041628</v>
+        <v>7041752</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4263,12 +4264,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4295,10 +4296,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121255058</v>
+        <v>121255053</v>
       </c>
       <c r="B37" t="n">
-        <v>91343</v>
+        <v>98081</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4311,34 +4312,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613546</v>
+        <v>613554</v>
       </c>
       <c r="R37" t="n">
-        <v>7041646</v>
+        <v>7041573</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4397,10 +4402,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121255010</v>
+        <v>121255046</v>
       </c>
       <c r="B38" t="n">
-        <v>90687</v>
+        <v>90717</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4413,21 +4418,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4437,10 +4442,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>613391</v>
+        <v>613534</v>
       </c>
       <c r="R38" t="n">
-        <v>7041765</v>
+        <v>7041558</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4467,12 +4472,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4499,10 +4504,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121255034</v>
+        <v>121255049</v>
       </c>
       <c r="B39" t="n">
-        <v>78598</v>
+        <v>91137</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4511,25 +4516,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4539,10 +4544,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>613618</v>
+        <v>613523</v>
       </c>
       <c r="R39" t="n">
-        <v>7041721</v>
+        <v>7041640</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4554,7 +4559,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4564,17 +4569,17 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4601,10 +4606,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121255012</v>
+        <v>121255024</v>
       </c>
       <c r="B40" t="n">
-        <v>90687</v>
+        <v>57367</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4617,34 +4622,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>613454</v>
+        <v>613541</v>
       </c>
       <c r="R40" t="n">
-        <v>7041671</v>
+        <v>7041685</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4703,10 +4713,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121255019</v>
+        <v>121255031</v>
       </c>
       <c r="B41" t="n">
-        <v>57348</v>
+        <v>90711</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4719,39 +4729,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>613528</v>
+        <v>613377</v>
       </c>
       <c r="R41" t="n">
-        <v>7041701</v>
+        <v>7041742</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4784,11 +4789,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4815,10 +4815,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121255043</v>
+        <v>121255039</v>
       </c>
       <c r="B42" t="n">
-        <v>90687</v>
+        <v>90662</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4827,25 +4827,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>613421</v>
+        <v>613386</v>
       </c>
       <c r="R42" t="n">
-        <v>7041692</v>
+        <v>7041700</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255008</v>
+        <v>121255054</v>
       </c>
       <c r="B3" t="n">
-        <v>90662</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613391</v>
+        <v>613568</v>
       </c>
       <c r="R3" t="n">
-        <v>7041765</v>
+        <v>7041618</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -832,7 +836,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -842,17 +846,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121255050</v>
+        <v>121255008</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>90662</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +895,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613348</v>
+        <v>613391</v>
       </c>
       <c r="R4" t="n">
-        <v>7041806</v>
+        <v>7041765</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -949,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,7 +967,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121255054</v>
+        <v>121255050</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -994,42 +997,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613568</v>
+        <v>613348</v>
       </c>
       <c r="R5" t="n">
-        <v>7041618</v>
+        <v>7041806</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1041,7 +1040,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1051,7 +1050,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1070,6 +1069,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121255037</v>
+        <v>121255026</v>
       </c>
       <c r="B14" t="n">
-        <v>90662</v>
+        <v>91137</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613554</v>
+        <v>613371</v>
       </c>
       <c r="R14" t="n">
-        <v>7041628</v>
+        <v>7041736</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1989,12 +1989,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121255006</v>
+        <v>121255016</v>
       </c>
       <c r="B15" t="n">
-        <v>74708</v>
+        <v>90697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613519</v>
+        <v>613505</v>
       </c>
       <c r="R15" t="n">
-        <v>7041683</v>
+        <v>7041675</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121255026</v>
+        <v>121255013</v>
       </c>
       <c r="B16" t="n">
-        <v>91137</v>
+        <v>90697</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613371</v>
+        <v>613465</v>
       </c>
       <c r="R16" t="n">
-        <v>7041736</v>
+        <v>7041678</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121255016</v>
+        <v>121255006</v>
       </c>
       <c r="B17" t="n">
-        <v>90697</v>
+        <v>74708</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613505</v>
+        <v>613519</v>
       </c>
       <c r="R17" t="n">
-        <v>7041675</v>
+        <v>7041683</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121255013</v>
+        <v>121255045</v>
       </c>
       <c r="B18" t="n">
-        <v>90697</v>
+        <v>56563</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2339,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613465</v>
+        <v>613481</v>
       </c>
       <c r="R18" t="n">
-        <v>7041678</v>
+        <v>7041555</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121255045</v>
+        <v>121255037</v>
       </c>
       <c r="B19" t="n">
-        <v>56563</v>
+        <v>90662</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613481</v>
+        <v>613554</v>
       </c>
       <c r="R19" t="n">
-        <v>7041555</v>
+        <v>7041628</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121255025</v>
+        <v>121255056</v>
       </c>
       <c r="B20" t="n">
-        <v>91137</v>
+        <v>98081</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,34 +2547,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613463</v>
+        <v>613391</v>
       </c>
       <c r="R20" t="n">
-        <v>7041737</v>
+        <v>7041785</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2601,12 +2605,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2633,10 +2637,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121255056</v>
+        <v>121255025</v>
       </c>
       <c r="B21" t="n">
-        <v>98081</v>
+        <v>91137</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,38 +2653,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613391</v>
+        <v>613463</v>
       </c>
       <c r="R21" t="n">
-        <v>7041785</v>
+        <v>7041737</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3675,10 +3675,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121255051</v>
+        <v>121255011</v>
       </c>
       <c r="B31" t="n">
-        <v>79682</v>
+        <v>90697</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613451</v>
+        <v>613415</v>
       </c>
       <c r="R31" t="n">
-        <v>7041510</v>
+        <v>7041708</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3745,12 +3745,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3777,7 +3777,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121255011</v>
+        <v>121255041</v>
       </c>
       <c r="B32" t="n">
         <v>90697</v>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613415</v>
+        <v>613536</v>
       </c>
       <c r="R32" t="n">
-        <v>7041708</v>
+        <v>7041639</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3847,12 +3847,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3879,10 +3879,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121255041</v>
+        <v>121255051</v>
       </c>
       <c r="B33" t="n">
-        <v>90697</v>
+        <v>79682</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>613536</v>
+        <v>613451</v>
       </c>
       <c r="R33" t="n">
-        <v>7041639</v>
+        <v>7041510</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4087,10 +4087,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121255048</v>
+        <v>121255032</v>
       </c>
       <c r="B35" t="n">
-        <v>57367</v>
+        <v>78601</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4103,39 +4103,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>613373</v>
+        <v>613446</v>
       </c>
       <c r="R35" t="n">
-        <v>7041694</v>
+        <v>7041752</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4162,12 +4157,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4194,10 +4189,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121255032</v>
+        <v>121255048</v>
       </c>
       <c r="B36" t="n">
-        <v>78601</v>
+        <v>57367</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4210,34 +4205,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613446</v>
+        <v>613373</v>
       </c>
       <c r="R36" t="n">
-        <v>7041752</v>
+        <v>7041694</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4264,12 +4264,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255054</v>
+        <v>121255008</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>90662</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613568</v>
+        <v>613391</v>
       </c>
       <c r="R3" t="n">
-        <v>7041618</v>
+        <v>7041765</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -836,7 +832,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -846,17 +842,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121255008</v>
+        <v>121255050</v>
       </c>
       <c r="B4" t="n">
-        <v>90662</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613391</v>
+        <v>613348</v>
       </c>
       <c r="R4" t="n">
-        <v>7041765</v>
+        <v>7041806</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -953,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -967,6 +963,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -985,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121255050</v>
+        <v>121255054</v>
       </c>
       <c r="B5" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,38 +994,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613348</v>
+        <v>613568</v>
       </c>
       <c r="R5" t="n">
-        <v>7041806</v>
+        <v>7041618</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1040,7 +1041,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1050,7 +1051,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1069,7 +1070,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121255019</v>
+        <v>121255023</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>57367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,16 +1410,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613528</v>
+        <v>613442</v>
       </c>
       <c r="R9" t="n">
-        <v>7041701</v>
+        <v>7041756</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1475,11 +1475,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1710,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121255021</v>
+        <v>121255019</v>
       </c>
       <c r="B12" t="n">
-        <v>79711</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,38 +1717,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613468</v>
+        <v>613528</v>
       </c>
       <c r="R12" t="n">
-        <v>7041729</v>
+        <v>7041701</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1786,6 +1786,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121255023</v>
+        <v>121255021</v>
       </c>
       <c r="B13" t="n">
-        <v>57367</v>
+        <v>79711</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,43 +1829,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613442</v>
+        <v>613468</v>
       </c>
       <c r="R13" t="n">
-        <v>7041756</v>
+        <v>7041729</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121255056</v>
+        <v>121255025</v>
       </c>
       <c r="B20" t="n">
-        <v>98081</v>
+        <v>91137</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,38 +2547,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613391</v>
+        <v>613463</v>
       </c>
       <c r="R20" t="n">
-        <v>7041785</v>
+        <v>7041737</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2605,12 +2601,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2637,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121255025</v>
+        <v>121255056</v>
       </c>
       <c r="B21" t="n">
-        <v>91137</v>
+        <v>98081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,34 +2649,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613463</v>
+        <v>613391</v>
       </c>
       <c r="R21" t="n">
-        <v>7041737</v>
+        <v>7041785</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3675,10 +3675,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121255011</v>
+        <v>121255051</v>
       </c>
       <c r="B31" t="n">
-        <v>90697</v>
+        <v>79682</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613415</v>
+        <v>613451</v>
       </c>
       <c r="R31" t="n">
-        <v>7041708</v>
+        <v>7041510</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3745,12 +3745,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3777,7 +3777,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121255041</v>
+        <v>121255011</v>
       </c>
       <c r="B32" t="n">
         <v>90697</v>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613536</v>
+        <v>613415</v>
       </c>
       <c r="R32" t="n">
-        <v>7041639</v>
+        <v>7041708</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3847,12 +3847,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3879,10 +3879,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121255051</v>
+        <v>121255041</v>
       </c>
       <c r="B33" t="n">
-        <v>79682</v>
+        <v>90697</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3895,21 +3895,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>613451</v>
+        <v>613536</v>
       </c>
       <c r="R33" t="n">
-        <v>7041510</v>
+        <v>7041639</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4087,10 +4087,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121255032</v>
+        <v>121255048</v>
       </c>
       <c r="B35" t="n">
-        <v>78601</v>
+        <v>57367</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4103,34 +4103,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>613446</v>
+        <v>613373</v>
       </c>
       <c r="R35" t="n">
-        <v>7041752</v>
+        <v>7041694</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4157,12 +4162,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4189,10 +4194,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121255048</v>
+        <v>121255032</v>
       </c>
       <c r="B36" t="n">
-        <v>57367</v>
+        <v>78601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4205,39 +4210,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613373</v>
+        <v>613446</v>
       </c>
       <c r="R36" t="n">
-        <v>7041694</v>
+        <v>7041752</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4264,12 +4264,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255040</v>
+        <v>121255006</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
+        <v>74708</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613542</v>
+        <v>613519</v>
       </c>
       <c r="R2" t="n">
-        <v>7041619</v>
+        <v>7041683</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255008</v>
+        <v>121255046</v>
       </c>
       <c r="B3" t="n">
-        <v>90662</v>
+        <v>90717</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613391</v>
+        <v>613534</v>
       </c>
       <c r="R3" t="n">
-        <v>7041765</v>
+        <v>7041558</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121255050</v>
+        <v>121255025</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>91137</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613348</v>
+        <v>613463</v>
       </c>
       <c r="R4" t="n">
-        <v>7041806</v>
+        <v>7041737</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,7 +963,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121255054</v>
+        <v>121255021</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>79711</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -994,42 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613568</v>
+        <v>613468</v>
       </c>
       <c r="R5" t="n">
-        <v>7041618</v>
+        <v>7041729</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1041,7 +1036,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1051,17 +1046,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121255057</v>
+        <v>121255019</v>
       </c>
       <c r="B6" t="n">
-        <v>90711</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,34 +1099,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613523</v>
+        <v>613528</v>
       </c>
       <c r="R6" t="n">
-        <v>7041633</v>
+        <v>7041701</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1158,12 +1158,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121255014</v>
+        <v>121255037</v>
       </c>
       <c r="B7" t="n">
-        <v>90697</v>
+        <v>90662</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613462</v>
+        <v>613554</v>
       </c>
       <c r="R7" t="n">
-        <v>7041669</v>
+        <v>7041628</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1260,12 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121255009</v>
+        <v>121255043</v>
       </c>
       <c r="B8" t="n">
         <v>90697</v>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613396</v>
+        <v>613421</v>
       </c>
       <c r="R8" t="n">
-        <v>7041771</v>
+        <v>7041692</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1362,12 +1367,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121255023</v>
+        <v>121255057</v>
       </c>
       <c r="B9" t="n">
-        <v>57367</v>
+        <v>90711</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,39 +1415,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613442</v>
+        <v>613523</v>
       </c>
       <c r="R9" t="n">
-        <v>7041756</v>
+        <v>7041633</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121255012</v>
+        <v>121255023</v>
       </c>
       <c r="B10" t="n">
-        <v>90697</v>
+        <v>57367</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,34 +1517,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613454</v>
+        <v>613442</v>
       </c>
       <c r="R10" t="n">
-        <v>7041671</v>
+        <v>7041756</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1603,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121255058</v>
+        <v>121255009</v>
       </c>
       <c r="B11" t="n">
-        <v>91353</v>
+        <v>90697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1620,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613546</v>
+        <v>613396</v>
       </c>
       <c r="R11" t="n">
-        <v>7041646</v>
+        <v>7041771</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1673,12 +1678,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121255019</v>
+        <v>121255014</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>90697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,39 +1726,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613528</v>
+        <v>613462</v>
       </c>
       <c r="R12" t="n">
-        <v>7041701</v>
+        <v>7041669</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1786,11 +1786,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121255021</v>
+        <v>121255050</v>
       </c>
       <c r="B13" t="n">
-        <v>79711</v>
+        <v>79682</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613468</v>
+        <v>613348</v>
       </c>
       <c r="R13" t="n">
-        <v>7041729</v>
+        <v>7041806</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1887,12 +1882,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1901,6 +1896,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1919,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121255026</v>
+        <v>121255053</v>
       </c>
       <c r="B14" t="n">
-        <v>91137</v>
+        <v>98081</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,34 +1931,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613371</v>
+        <v>613554</v>
       </c>
       <c r="R14" t="n">
-        <v>7041736</v>
+        <v>7041573</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1989,12 +1989,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121255016</v>
+        <v>121255054</v>
       </c>
       <c r="B15" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,38 +2033,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613505</v>
+        <v>613568</v>
       </c>
       <c r="R15" t="n">
-        <v>7041675</v>
+        <v>7041618</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2076,7 +2080,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2086,17 +2090,17 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2123,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121255013</v>
+        <v>121255048</v>
       </c>
       <c r="B16" t="n">
-        <v>90697</v>
+        <v>57367</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,34 +2143,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613465</v>
+        <v>613373</v>
       </c>
       <c r="R16" t="n">
-        <v>7041678</v>
+        <v>7041694</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2193,12 +2202,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121255006</v>
+        <v>121255011</v>
       </c>
       <c r="B17" t="n">
-        <v>74708</v>
+        <v>90697</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,21 +2250,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613519</v>
+        <v>613415</v>
       </c>
       <c r="R17" t="n">
-        <v>7041683</v>
+        <v>7041708</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2327,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121255045</v>
+        <v>121255042</v>
       </c>
       <c r="B18" t="n">
-        <v>56563</v>
+        <v>90697</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2348,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613481</v>
+        <v>613460</v>
       </c>
       <c r="R18" t="n">
-        <v>7041555</v>
+        <v>7041672</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2429,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121255037</v>
+        <v>121255056</v>
       </c>
       <c r="B19" t="n">
-        <v>90662</v>
+        <v>98081</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,38 +2450,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613554</v>
+        <v>613391</v>
       </c>
       <c r="R19" t="n">
-        <v>7041628</v>
+        <v>7041785</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2531,10 +2544,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121255025</v>
+        <v>121255012</v>
       </c>
       <c r="B20" t="n">
-        <v>91137</v>
+        <v>90697</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,25 +2556,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2584,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613463</v>
+        <v>613454</v>
       </c>
       <c r="R20" t="n">
-        <v>7041737</v>
+        <v>7041671</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2633,10 +2646,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121255056</v>
+        <v>121255031</v>
       </c>
       <c r="B21" t="n">
-        <v>98081</v>
+        <v>90711</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,42 +2658,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613391</v>
+        <v>613377</v>
       </c>
       <c r="R21" t="n">
-        <v>7041785</v>
+        <v>7041742</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2707,12 +2716,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2739,10 +2748,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121255034</v>
+        <v>121255013</v>
       </c>
       <c r="B22" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2755,21 +2764,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2779,10 +2788,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613618</v>
+        <v>613465</v>
       </c>
       <c r="R22" t="n">
-        <v>7041721</v>
+        <v>7041678</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2794,7 +2803,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2804,7 +2813,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2841,10 +2850,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121255038</v>
+        <v>121255024</v>
       </c>
       <c r="B23" t="n">
-        <v>90662</v>
+        <v>57367</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,38 +2862,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613396</v>
+        <v>613541</v>
       </c>
       <c r="R23" t="n">
-        <v>7041694</v>
+        <v>7041685</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2911,12 +2925,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2943,10 +2957,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121255029</v>
+        <v>121255049</v>
       </c>
       <c r="B24" t="n">
-        <v>98081</v>
+        <v>91137</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,38 +2973,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613510</v>
+        <v>613523</v>
       </c>
       <c r="R24" t="n">
-        <v>7041675</v>
+        <v>7041640</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3017,12 +3027,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3049,10 +3059,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121255055</v>
+        <v>121255034</v>
       </c>
       <c r="B25" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3061,42 +3071,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613400</v>
+        <v>613618</v>
       </c>
       <c r="R25" t="n">
-        <v>7041781</v>
+        <v>7041721</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3108,7 +3114,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3118,17 +3124,17 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3155,10 +3161,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121255044</v>
+        <v>121255032</v>
       </c>
       <c r="B26" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3171,39 +3177,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>613475</v>
+        <v>613446</v>
       </c>
       <c r="R26" t="n">
-        <v>7041662</v>
+        <v>7041752</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3230,17 +3231,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3267,7 +3263,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121255043</v>
+        <v>121255040</v>
       </c>
       <c r="B27" t="n">
         <v>90697</v>
@@ -3307,10 +3303,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>613421</v>
+        <v>613542</v>
       </c>
       <c r="R27" t="n">
-        <v>7041692</v>
+        <v>7041619</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3369,10 +3365,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121255010</v>
+        <v>121255038</v>
       </c>
       <c r="B28" t="n">
-        <v>90697</v>
+        <v>90662</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3381,25 +3377,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3409,10 +3405,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613391</v>
+        <v>613396</v>
       </c>
       <c r="R28" t="n">
-        <v>7041765</v>
+        <v>7041694</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3439,12 +3435,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3471,10 +3467,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121255042</v>
+        <v>121255055</v>
       </c>
       <c r="B29" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3483,38 +3479,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613460</v>
+        <v>613400</v>
       </c>
       <c r="R29" t="n">
-        <v>7041672</v>
+        <v>7041781</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121255015</v>
+        <v>121255044</v>
       </c>
       <c r="B30" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3589,34 +3589,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613481</v>
+        <v>613475</v>
       </c>
       <c r="R30" t="n">
-        <v>7041676</v>
+        <v>7041662</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3643,12 +3648,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3675,10 +3685,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121255051</v>
+        <v>121255052</v>
       </c>
       <c r="B31" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3687,38 +3697,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613451</v>
+        <v>613542</v>
       </c>
       <c r="R31" t="n">
-        <v>7041510</v>
+        <v>7041572</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3777,7 +3791,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121255011</v>
+        <v>121255016</v>
       </c>
       <c r="B32" t="n">
         <v>90697</v>
@@ -3817,10 +3831,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613415</v>
+        <v>613505</v>
       </c>
       <c r="R32" t="n">
-        <v>7041708</v>
+        <v>7041675</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3879,10 +3893,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121255041</v>
+        <v>121255058</v>
       </c>
       <c r="B33" t="n">
-        <v>90697</v>
+        <v>91353</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3891,25 +3905,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3919,10 +3933,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>613536</v>
+        <v>613546</v>
       </c>
       <c r="R33" t="n">
-        <v>7041639</v>
+        <v>7041646</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3981,10 +3995,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121255052</v>
+        <v>121255015</v>
       </c>
       <c r="B34" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3993,42 +4007,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>613542</v>
+        <v>613481</v>
       </c>
       <c r="R34" t="n">
-        <v>7041572</v>
+        <v>7041676</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4055,12 +4065,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4087,10 +4097,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121255048</v>
+        <v>121255041</v>
       </c>
       <c r="B35" t="n">
-        <v>57367</v>
+        <v>90697</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4103,39 +4113,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>613373</v>
+        <v>613536</v>
       </c>
       <c r="R35" t="n">
-        <v>7041694</v>
+        <v>7041639</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4194,10 +4199,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121255032</v>
+        <v>121255039</v>
       </c>
       <c r="B36" t="n">
-        <v>78601</v>
+        <v>90662</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4206,25 +4211,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4234,10 +4239,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613446</v>
+        <v>613386</v>
       </c>
       <c r="R36" t="n">
-        <v>7041752</v>
+        <v>7041700</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4264,12 +4269,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4296,10 +4301,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121255053</v>
+        <v>121255010</v>
       </c>
       <c r="B37" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4308,42 +4313,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613554</v>
+        <v>613391</v>
       </c>
       <c r="R37" t="n">
-        <v>7041573</v>
+        <v>7041765</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4370,12 +4371,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4402,10 +4403,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121255046</v>
+        <v>121255051</v>
       </c>
       <c r="B38" t="n">
-        <v>90717</v>
+        <v>79682</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4418,21 +4419,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4442,10 +4443,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>613534</v>
+        <v>613451</v>
       </c>
       <c r="R38" t="n">
-        <v>7041558</v>
+        <v>7041510</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4504,10 +4505,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121255049</v>
+        <v>121255008</v>
       </c>
       <c r="B39" t="n">
-        <v>91137</v>
+        <v>90662</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4516,25 +4517,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4544,10 +4545,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>613523</v>
+        <v>613391</v>
       </c>
       <c r="R39" t="n">
-        <v>7041640</v>
+        <v>7041765</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4574,12 +4575,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4606,10 +4607,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121255024</v>
+        <v>121255045</v>
       </c>
       <c r="B40" t="n">
-        <v>57367</v>
+        <v>56563</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4618,43 +4619,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>613541</v>
+        <v>613481</v>
       </c>
       <c r="R40" t="n">
-        <v>7041685</v>
+        <v>7041555</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4681,12 +4677,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4713,10 +4709,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121255031</v>
+        <v>121255029</v>
       </c>
       <c r="B41" t="n">
-        <v>90711</v>
+        <v>98081</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4725,38 +4721,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>613377</v>
+        <v>613510</v>
       </c>
       <c r="R41" t="n">
-        <v>7041742</v>
+        <v>7041675</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4815,10 +4815,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121255039</v>
+        <v>121255026</v>
       </c>
       <c r="B42" t="n">
-        <v>90662</v>
+        <v>91137</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4827,25 +4827,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>613386</v>
+        <v>613371</v>
       </c>
       <c r="R42" t="n">
-        <v>7041700</v>
+        <v>7041736</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121255037</v>
+        <v>121255043</v>
       </c>
       <c r="B7" t="n">
-        <v>90662</v>
+        <v>90697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613554</v>
+        <v>613421</v>
       </c>
       <c r="R7" t="n">
-        <v>7041628</v>
+        <v>7041692</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121255043</v>
+        <v>121255057</v>
       </c>
       <c r="B8" t="n">
-        <v>90697</v>
+        <v>90711</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613421</v>
+        <v>613523</v>
       </c>
       <c r="R8" t="n">
-        <v>7041692</v>
+        <v>7041633</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121255057</v>
+        <v>121255037</v>
       </c>
       <c r="B9" t="n">
-        <v>90711</v>
+        <v>90662</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613523</v>
+        <v>613554</v>
       </c>
       <c r="R9" t="n">
-        <v>7041633</v>
+        <v>7041628</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121255050</v>
+        <v>121255048</v>
       </c>
       <c r="B13" t="n">
-        <v>79682</v>
+        <v>57367</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,34 +1828,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613348</v>
+        <v>613373</v>
       </c>
       <c r="R13" t="n">
-        <v>7041806</v>
+        <v>7041694</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1896,7 +1901,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2127,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121255048</v>
+        <v>121255050</v>
       </c>
       <c r="B16" t="n">
-        <v>57367</v>
+        <v>79682</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,39 +2147,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613373</v>
+        <v>613348</v>
       </c>
       <c r="R16" t="n">
-        <v>7041694</v>
+        <v>7041806</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2216,6 +2215,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121255011</v>
+        <v>121255056</v>
       </c>
       <c r="B17" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,38 +2246,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613415</v>
+        <v>613391</v>
       </c>
       <c r="R17" t="n">
-        <v>7041708</v>
+        <v>7041785</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2304,12 +2308,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2336,7 +2340,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121255042</v>
+        <v>121255011</v>
       </c>
       <c r="B18" t="n">
         <v>90697</v>
@@ -2376,10 +2380,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613460</v>
+        <v>613415</v>
       </c>
       <c r="R18" t="n">
-        <v>7041672</v>
+        <v>7041708</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2406,12 +2410,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2438,10 +2442,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121255056</v>
+        <v>121255042</v>
       </c>
       <c r="B19" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,42 +2454,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613391</v>
+        <v>613460</v>
       </c>
       <c r="R19" t="n">
-        <v>7041785</v>
+        <v>7041672</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -4607,10 +4607,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121255045</v>
+        <v>121255029</v>
       </c>
       <c r="B40" t="n">
-        <v>56563</v>
+        <v>98081</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4619,38 +4619,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>613481</v>
+        <v>613510</v>
       </c>
       <c r="R40" t="n">
-        <v>7041555</v>
+        <v>7041675</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4677,12 +4681,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4709,10 +4713,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121255029</v>
+        <v>121255045</v>
       </c>
       <c r="B41" t="n">
-        <v>98081</v>
+        <v>56563</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4721,42 +4725,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>613510</v>
+        <v>613481</v>
       </c>
       <c r="R41" t="n">
-        <v>7041675</v>
+        <v>7041555</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4783,12 +4783,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255006</v>
+        <v>121255042</v>
       </c>
       <c r="B2" t="n">
-        <v>74708</v>
+        <v>90709</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613519</v>
+        <v>613460</v>
       </c>
       <c r="R2" t="n">
-        <v>7041683</v>
+        <v>7041672</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255046</v>
+        <v>121255031</v>
       </c>
       <c r="B3" t="n">
-        <v>90717</v>
+        <v>90723</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613534</v>
+        <v>613377</v>
       </c>
       <c r="R3" t="n">
-        <v>7041558</v>
+        <v>7041742</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121255025</v>
+        <v>121255046</v>
       </c>
       <c r="B4" t="n">
-        <v>91137</v>
+        <v>90729</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613463</v>
+        <v>613534</v>
       </c>
       <c r="R4" t="n">
-        <v>7041737</v>
+        <v>7041558</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121255021</v>
+        <v>121255008</v>
       </c>
       <c r="B5" t="n">
-        <v>79711</v>
+        <v>90674</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613468</v>
+        <v>613391</v>
       </c>
       <c r="R5" t="n">
-        <v>7041729</v>
+        <v>7041765</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121255019</v>
+        <v>121255032</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,39 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613528</v>
+        <v>613446</v>
       </c>
       <c r="R6" t="n">
-        <v>7041701</v>
+        <v>7041752</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1164,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121255043</v>
+        <v>121255021</v>
       </c>
       <c r="B7" t="n">
-        <v>90697</v>
+        <v>79714</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613421</v>
+        <v>613468</v>
       </c>
       <c r="R7" t="n">
-        <v>7041692</v>
+        <v>7041729</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1265,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121255057</v>
+        <v>121255052</v>
       </c>
       <c r="B8" t="n">
-        <v>90711</v>
+        <v>98094</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,38 +1299,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613523</v>
+        <v>613542</v>
       </c>
       <c r="R8" t="n">
-        <v>7041633</v>
+        <v>7041572</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1399,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121255037</v>
+        <v>121255058</v>
       </c>
       <c r="B9" t="n">
-        <v>90662</v>
+        <v>91365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1405,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>898</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613554</v>
+        <v>613546</v>
       </c>
       <c r="R9" t="n">
-        <v>7041628</v>
+        <v>7041646</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1501,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121255023</v>
+        <v>121255038</v>
       </c>
       <c r="B10" t="n">
-        <v>57367</v>
+        <v>90674</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,43 +1507,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613442</v>
+        <v>613396</v>
       </c>
       <c r="R10" t="n">
-        <v>7041756</v>
+        <v>7041694</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1576,12 +1565,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121255009</v>
+        <v>121255006</v>
       </c>
       <c r="B11" t="n">
-        <v>90697</v>
+        <v>74710</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613396</v>
+        <v>613519</v>
       </c>
       <c r="R11" t="n">
-        <v>7041771</v>
+        <v>7041683</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1710,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121255014</v>
+        <v>121255048</v>
       </c>
       <c r="B12" t="n">
-        <v>90697</v>
+        <v>57367</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,34 +1715,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613462</v>
+        <v>613373</v>
       </c>
       <c r="R12" t="n">
-        <v>7041669</v>
+        <v>7041694</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1780,12 +1774,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121255048</v>
+        <v>121255039</v>
       </c>
       <c r="B13" t="n">
-        <v>57367</v>
+        <v>90674</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,43 +1818,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613373</v>
+        <v>613386</v>
       </c>
       <c r="R13" t="n">
-        <v>7041694</v>
+        <v>7041700</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1919,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121255053</v>
+        <v>121255012</v>
       </c>
       <c r="B14" t="n">
-        <v>98081</v>
+        <v>90709</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,42 +1920,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613554</v>
+        <v>613454</v>
       </c>
       <c r="R14" t="n">
-        <v>7041573</v>
+        <v>7041671</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1993,12 +1978,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2025,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121255054</v>
+        <v>121255016</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>90709</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,42 +2022,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613568</v>
+        <v>613505</v>
       </c>
       <c r="R15" t="n">
-        <v>7041618</v>
+        <v>7041675</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2084,7 +2065,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2094,17 +2075,17 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2131,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121255050</v>
+        <v>121255015</v>
       </c>
       <c r="B16" t="n">
-        <v>79682</v>
+        <v>90709</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2147,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613348</v>
+        <v>613481</v>
       </c>
       <c r="R16" t="n">
-        <v>7041806</v>
+        <v>7041676</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2201,12 +2182,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,7 +2196,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2234,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121255056</v>
+        <v>121255024</v>
       </c>
       <c r="B17" t="n">
-        <v>98081</v>
+        <v>57367</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,30 +2226,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>150</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2278,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613391</v>
+        <v>613541</v>
       </c>
       <c r="R17" t="n">
-        <v>7041785</v>
+        <v>7041685</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2308,12 +2289,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2340,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121255011</v>
+        <v>121255050</v>
       </c>
       <c r="B18" t="n">
-        <v>90697</v>
+        <v>79685</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2356,21 +2337,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2380,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613415</v>
+        <v>613348</v>
       </c>
       <c r="R18" t="n">
-        <v>7041708</v>
+        <v>7041806</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2410,12 +2391,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2424,6 +2405,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2442,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121255042</v>
+        <v>121255023</v>
       </c>
       <c r="B19" t="n">
-        <v>90697</v>
+        <v>57367</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2458,34 +2440,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613460</v>
+        <v>613442</v>
       </c>
       <c r="R19" t="n">
-        <v>7041672</v>
+        <v>7041756</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2512,12 +2499,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2544,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121255012</v>
+        <v>121255013</v>
       </c>
       <c r="B20" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2584,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613454</v>
+        <v>613465</v>
       </c>
       <c r="R20" t="n">
-        <v>7041671</v>
+        <v>7041678</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2646,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121255031</v>
+        <v>121255011</v>
       </c>
       <c r="B21" t="n">
-        <v>90711</v>
+        <v>90709</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2662,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2686,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613377</v>
+        <v>613415</v>
       </c>
       <c r="R21" t="n">
-        <v>7041742</v>
+        <v>7041708</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2748,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121255013</v>
+        <v>121255041</v>
       </c>
       <c r="B22" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2788,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613465</v>
+        <v>613536</v>
       </c>
       <c r="R22" t="n">
-        <v>7041678</v>
+        <v>7041639</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2818,12 +2805,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2850,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121255024</v>
+        <v>121255019</v>
       </c>
       <c r="B23" t="n">
-        <v>57367</v>
+        <v>57351</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2866,16 +2853,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2886,7 +2873,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2895,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613541</v>
+        <v>613528</v>
       </c>
       <c r="R23" t="n">
-        <v>7041685</v>
+        <v>7041701</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2931,6 +2918,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2957,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121255049</v>
+        <v>121255043</v>
       </c>
       <c r="B24" t="n">
-        <v>91137</v>
+        <v>90709</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2969,25 +2961,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2997,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613523</v>
+        <v>613421</v>
       </c>
       <c r="R24" t="n">
-        <v>7041640</v>
+        <v>7041692</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3059,10 +3051,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121255034</v>
+        <v>121255037</v>
       </c>
       <c r="B25" t="n">
-        <v>78601</v>
+        <v>90674</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3071,25 +3063,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3099,10 +3091,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613618</v>
+        <v>613554</v>
       </c>
       <c r="R25" t="n">
-        <v>7041721</v>
+        <v>7041628</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3114,7 +3106,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3124,17 +3116,17 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3161,10 +3153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121255032</v>
+        <v>121255025</v>
       </c>
       <c r="B26" t="n">
-        <v>78601</v>
+        <v>91149</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3173,25 +3165,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3201,10 +3193,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>613446</v>
+        <v>613463</v>
       </c>
       <c r="R26" t="n">
-        <v>7041752</v>
+        <v>7041737</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3263,10 +3255,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121255040</v>
+        <v>121255034</v>
       </c>
       <c r="B27" t="n">
-        <v>90697</v>
+        <v>78604</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3279,21 +3271,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3303,10 +3295,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>613542</v>
+        <v>613618</v>
       </c>
       <c r="R27" t="n">
-        <v>7041619</v>
+        <v>7041721</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3318,7 +3310,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3328,17 +3320,17 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3365,10 +3357,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121255038</v>
+        <v>121255045</v>
       </c>
       <c r="B28" t="n">
-        <v>90662</v>
+        <v>56563</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3381,21 +3373,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3405,10 +3397,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613396</v>
+        <v>613481</v>
       </c>
       <c r="R28" t="n">
-        <v>7041694</v>
+        <v>7041555</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3467,10 +3459,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121255055</v>
+        <v>121255029</v>
       </c>
       <c r="B29" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3511,10 +3503,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613400</v>
+        <v>613510</v>
       </c>
       <c r="R29" t="n">
-        <v>7041781</v>
+        <v>7041675</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3541,12 +3533,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3573,10 +3565,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121255044</v>
+        <v>121255051</v>
       </c>
       <c r="B30" t="n">
-        <v>57351</v>
+        <v>79685</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3589,39 +3581,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613475</v>
+        <v>613451</v>
       </c>
       <c r="R30" t="n">
-        <v>7041662</v>
+        <v>7041510</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3654,11 +3641,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3685,10 +3667,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121255052</v>
+        <v>121255010</v>
       </c>
       <c r="B31" t="n">
-        <v>98081</v>
+        <v>90709</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3697,42 +3679,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613542</v>
+        <v>613391</v>
       </c>
       <c r="R31" t="n">
-        <v>7041572</v>
+        <v>7041765</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3759,12 +3737,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3791,10 +3769,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121255016</v>
+        <v>121255055</v>
       </c>
       <c r="B32" t="n">
-        <v>90697</v>
+        <v>98094</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3803,38 +3781,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613505</v>
+        <v>613400</v>
       </c>
       <c r="R32" t="n">
-        <v>7041675</v>
+        <v>7041781</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3861,12 +3843,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3893,10 +3875,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121255058</v>
+        <v>121255053</v>
       </c>
       <c r="B33" t="n">
-        <v>91353</v>
+        <v>98094</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3909,34 +3891,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>613546</v>
+        <v>613554</v>
       </c>
       <c r="R33" t="n">
-        <v>7041646</v>
+        <v>7041573</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3995,10 +3981,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121255015</v>
+        <v>121255049</v>
       </c>
       <c r="B34" t="n">
-        <v>90697</v>
+        <v>91149</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4007,25 +3993,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4035,10 +4021,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>613481</v>
+        <v>613523</v>
       </c>
       <c r="R34" t="n">
-        <v>7041676</v>
+        <v>7041640</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4065,12 +4051,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4097,10 +4083,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121255041</v>
+        <v>121255054</v>
       </c>
       <c r="B35" t="n">
-        <v>90697</v>
+        <v>98094</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4109,38 +4095,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>613536</v>
+        <v>613568</v>
       </c>
       <c r="R35" t="n">
-        <v>7041639</v>
+        <v>7041618</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4152,7 +4142,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4162,7 +4152,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4199,10 +4189,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121255039</v>
+        <v>121255044</v>
       </c>
       <c r="B36" t="n">
-        <v>90662</v>
+        <v>57351</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4211,38 +4201,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613386</v>
+        <v>613475</v>
       </c>
       <c r="R36" t="n">
-        <v>7041700</v>
+        <v>7041662</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4275,6 +4270,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4301,10 +4301,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121255010</v>
+        <v>121255040</v>
       </c>
       <c r="B37" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613391</v>
+        <v>613542</v>
       </c>
       <c r="R37" t="n">
-        <v>7041765</v>
+        <v>7041619</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4403,10 +4403,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121255051</v>
+        <v>121255026</v>
       </c>
       <c r="B38" t="n">
-        <v>79682</v>
+        <v>91149</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4415,25 +4415,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>613451</v>
+        <v>613371</v>
       </c>
       <c r="R38" t="n">
-        <v>7041510</v>
+        <v>7041736</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4473,12 +4473,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4505,10 +4505,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121255008</v>
+        <v>121255056</v>
       </c>
       <c r="B39" t="n">
-        <v>90662</v>
+        <v>98094</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4517,28 +4517,32 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
@@ -4548,7 +4552,7 @@
         <v>613391</v>
       </c>
       <c r="R39" t="n">
-        <v>7041765</v>
+        <v>7041785</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4575,12 +4579,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4607,10 +4611,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121255029</v>
+        <v>121255057</v>
       </c>
       <c r="B40" t="n">
-        <v>98081</v>
+        <v>90723</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4619,42 +4623,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>613510</v>
+        <v>613523</v>
       </c>
       <c r="R40" t="n">
-        <v>7041675</v>
+        <v>7041633</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4681,12 +4681,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4713,10 +4713,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121255045</v>
+        <v>121255014</v>
       </c>
       <c r="B41" t="n">
-        <v>56563</v>
+        <v>90709</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4725,25 +4725,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>613481</v>
+        <v>613462</v>
       </c>
       <c r="R41" t="n">
-        <v>7041555</v>
+        <v>7041669</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4783,12 +4783,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4815,10 +4815,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121255026</v>
+        <v>121255009</v>
       </c>
       <c r="B42" t="n">
-        <v>91137</v>
+        <v>90709</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4827,25 +4827,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>613371</v>
+        <v>613396</v>
       </c>
       <c r="R42" t="n">
-        <v>7041736</v>
+        <v>7041771</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255042</v>
+        <v>121255046</v>
       </c>
       <c r="B2" t="n">
-        <v>90709</v>
+        <v>90730</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613460</v>
+        <v>613534</v>
       </c>
       <c r="R2" t="n">
-        <v>7041672</v>
+        <v>7041558</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255031</v>
+        <v>121255037</v>
       </c>
       <c r="B3" t="n">
-        <v>90723</v>
+        <v>90675</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613377</v>
+        <v>613554</v>
       </c>
       <c r="R3" t="n">
-        <v>7041742</v>
+        <v>7041628</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121255046</v>
+        <v>121255053</v>
       </c>
       <c r="B4" t="n">
-        <v>90729</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613534</v>
+        <v>613554</v>
       </c>
       <c r="R4" t="n">
-        <v>7041558</v>
+        <v>7041573</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121255008</v>
+        <v>121255055</v>
       </c>
       <c r="B5" t="n">
-        <v>90674</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +997,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613391</v>
+        <v>613400</v>
       </c>
       <c r="R5" t="n">
-        <v>7041765</v>
+        <v>7041781</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1051,12 +1059,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121255032</v>
+        <v>121255056</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1103,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613446</v>
+        <v>613391</v>
       </c>
       <c r="R6" t="n">
-        <v>7041752</v>
+        <v>7041785</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1153,12 +1165,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121255021</v>
+        <v>121255006</v>
       </c>
       <c r="B7" t="n">
-        <v>79714</v>
+        <v>74710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1209,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613468</v>
+        <v>613519</v>
       </c>
       <c r="R7" t="n">
-        <v>7041729</v>
+        <v>7041683</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121255052</v>
+        <v>121255040</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>90710</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,32 +1311,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
@@ -1334,7 +1342,7 @@
         <v>613542</v>
       </c>
       <c r="R8" t="n">
-        <v>7041572</v>
+        <v>7041619</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1393,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121255058</v>
+        <v>121255041</v>
       </c>
       <c r="B9" t="n">
-        <v>91365</v>
+        <v>90710</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,25 +1413,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613546</v>
+        <v>613536</v>
       </c>
       <c r="R9" t="n">
-        <v>7041646</v>
+        <v>7041639</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1495,10 +1503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121255038</v>
+        <v>121255008</v>
       </c>
       <c r="B10" t="n">
-        <v>90674</v>
+        <v>90675</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613396</v>
+        <v>613391</v>
       </c>
       <c r="R10" t="n">
-        <v>7041694</v>
+        <v>7041765</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1565,12 +1573,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,10 +1605,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121255006</v>
+        <v>121255045</v>
       </c>
       <c r="B11" t="n">
-        <v>74710</v>
+        <v>56563</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,25 +1617,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1645,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613519</v>
+        <v>613481</v>
       </c>
       <c r="R11" t="n">
-        <v>7041683</v>
+        <v>7041555</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1667,12 +1675,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1699,10 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121255048</v>
+        <v>121255015</v>
       </c>
       <c r="B12" t="n">
-        <v>57367</v>
+        <v>90710</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1715,39 +1723,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613373</v>
+        <v>613481</v>
       </c>
       <c r="R12" t="n">
-        <v>7041694</v>
+        <v>7041676</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1774,12 +1777,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1806,10 +1809,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121255039</v>
+        <v>121255051</v>
       </c>
       <c r="B13" t="n">
-        <v>90674</v>
+        <v>79685</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,25 +1821,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613386</v>
+        <v>613451</v>
       </c>
       <c r="R13" t="n">
-        <v>7041700</v>
+        <v>7041510</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1908,10 +1911,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121255012</v>
+        <v>121255054</v>
       </c>
       <c r="B14" t="n">
-        <v>90709</v>
+        <v>98095</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,38 +1923,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613454</v>
+        <v>613568</v>
       </c>
       <c r="R14" t="n">
-        <v>7041671</v>
+        <v>7041618</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1963,7 +1970,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1973,17 +1980,17 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2010,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121255016</v>
+        <v>121255050</v>
       </c>
       <c r="B15" t="n">
-        <v>90709</v>
+        <v>79685</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2033,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613505</v>
+        <v>613348</v>
       </c>
       <c r="R15" t="n">
-        <v>7041675</v>
+        <v>7041806</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2080,12 +2087,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2094,6 +2101,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2112,10 +2120,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121255015</v>
+        <v>121255016</v>
       </c>
       <c r="B16" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2152,10 +2160,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613481</v>
+        <v>613505</v>
       </c>
       <c r="R16" t="n">
-        <v>7041676</v>
+        <v>7041675</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2214,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121255024</v>
+        <v>121255031</v>
       </c>
       <c r="B17" t="n">
-        <v>57367</v>
+        <v>90724</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,39 +2238,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613541</v>
+        <v>613377</v>
       </c>
       <c r="R17" t="n">
-        <v>7041685</v>
+        <v>7041742</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2321,10 +2324,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121255050</v>
+        <v>121255048</v>
       </c>
       <c r="B18" t="n">
-        <v>79685</v>
+        <v>57367</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,34 +2340,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613348</v>
+        <v>613373</v>
       </c>
       <c r="R18" t="n">
-        <v>7041806</v>
+        <v>7041694</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2405,7 +2413,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2424,10 +2431,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121255023</v>
+        <v>121255025</v>
       </c>
       <c r="B19" t="n">
-        <v>57367</v>
+        <v>91150</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2436,43 +2443,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613442</v>
+        <v>613463</v>
       </c>
       <c r="R19" t="n">
-        <v>7041756</v>
+        <v>7041737</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2531,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121255013</v>
+        <v>121255039</v>
       </c>
       <c r="B20" t="n">
-        <v>90709</v>
+        <v>90675</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,25 +2545,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2573,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613465</v>
+        <v>613386</v>
       </c>
       <c r="R20" t="n">
-        <v>7041678</v>
+        <v>7041700</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2601,12 +2603,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2633,10 +2635,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121255011</v>
+        <v>121255014</v>
       </c>
       <c r="B21" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2673,10 +2675,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613415</v>
+        <v>613462</v>
       </c>
       <c r="R21" t="n">
-        <v>7041708</v>
+        <v>7041669</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2735,10 +2737,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121255041</v>
+        <v>121255034</v>
       </c>
       <c r="B22" t="n">
-        <v>90709</v>
+        <v>78604</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2753,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2777,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613536</v>
+        <v>613618</v>
       </c>
       <c r="R22" t="n">
-        <v>7041639</v>
+        <v>7041721</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2790,7 +2792,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2800,17 +2802,17 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,10 +2839,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121255019</v>
+        <v>121255032</v>
       </c>
       <c r="B23" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,39 +2855,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613528</v>
+        <v>613446</v>
       </c>
       <c r="R23" t="n">
-        <v>7041701</v>
+        <v>7041752</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2918,11 +2915,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2949,10 +2941,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121255043</v>
+        <v>121255012</v>
       </c>
       <c r="B24" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2989,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613421</v>
+        <v>613454</v>
       </c>
       <c r="R24" t="n">
-        <v>7041692</v>
+        <v>7041671</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3019,12 +3011,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3051,10 +3043,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121255037</v>
+        <v>121255044</v>
       </c>
       <c r="B25" t="n">
-        <v>90674</v>
+        <v>57351</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3063,38 +3055,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613554</v>
+        <v>613475</v>
       </c>
       <c r="R25" t="n">
-        <v>7041628</v>
+        <v>7041662</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3127,6 +3124,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3153,10 +3155,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121255025</v>
+        <v>121255021</v>
       </c>
       <c r="B26" t="n">
-        <v>91149</v>
+        <v>79714</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3165,25 +3167,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3193,10 +3195,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>613463</v>
+        <v>613468</v>
       </c>
       <c r="R26" t="n">
-        <v>7041737</v>
+        <v>7041729</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3255,10 +3257,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121255034</v>
+        <v>121255009</v>
       </c>
       <c r="B27" t="n">
-        <v>78604</v>
+        <v>90710</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3271,21 +3273,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3295,10 +3297,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>613618</v>
+        <v>613396</v>
       </c>
       <c r="R27" t="n">
-        <v>7041721</v>
+        <v>7041771</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3310,7 +3312,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3320,7 +3322,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3357,10 +3359,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121255045</v>
+        <v>121255013</v>
       </c>
       <c r="B28" t="n">
-        <v>56563</v>
+        <v>90710</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3369,25 +3371,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3397,10 +3399,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613481</v>
+        <v>613465</v>
       </c>
       <c r="R28" t="n">
-        <v>7041555</v>
+        <v>7041678</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3427,12 +3429,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3459,10 +3461,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121255029</v>
+        <v>121255042</v>
       </c>
       <c r="B29" t="n">
-        <v>98094</v>
+        <v>90710</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3471,42 +3473,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613510</v>
+        <v>613460</v>
       </c>
       <c r="R29" t="n">
-        <v>7041675</v>
+        <v>7041672</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3533,12 +3531,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3565,10 +3563,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121255051</v>
+        <v>121255010</v>
       </c>
       <c r="B30" t="n">
-        <v>79685</v>
+        <v>90710</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3581,21 +3579,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3605,10 +3603,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613451</v>
+        <v>613391</v>
       </c>
       <c r="R30" t="n">
-        <v>7041510</v>
+        <v>7041765</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3635,12 +3633,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3667,10 +3665,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121255010</v>
+        <v>121255058</v>
       </c>
       <c r="B31" t="n">
-        <v>90709</v>
+        <v>91366</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3679,25 +3677,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3707,10 +3705,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613391</v>
+        <v>613546</v>
       </c>
       <c r="R31" t="n">
-        <v>7041765</v>
+        <v>7041646</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3737,12 +3735,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3769,10 +3767,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121255055</v>
+        <v>121255019</v>
       </c>
       <c r="B32" t="n">
-        <v>98094</v>
+        <v>57351</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3781,30 +3779,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3813,10 +3812,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613400</v>
+        <v>613528</v>
       </c>
       <c r="R32" t="n">
-        <v>7041781</v>
+        <v>7041701</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3843,12 +3842,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3875,10 +3879,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121255053</v>
+        <v>121255057</v>
       </c>
       <c r="B33" t="n">
-        <v>98094</v>
+        <v>90724</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3887,42 +3891,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>613554</v>
+        <v>613523</v>
       </c>
       <c r="R33" t="n">
-        <v>7041573</v>
+        <v>7041633</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3981,10 +3981,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121255049</v>
+        <v>121255024</v>
       </c>
       <c r="B34" t="n">
-        <v>91149</v>
+        <v>57367</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3993,38 +3993,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>613523</v>
+        <v>613541</v>
       </c>
       <c r="R34" t="n">
-        <v>7041640</v>
+        <v>7041685</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4051,12 +4056,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4083,10 +4088,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121255054</v>
+        <v>121255043</v>
       </c>
       <c r="B35" t="n">
-        <v>98094</v>
+        <v>90710</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4095,42 +4100,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>613568</v>
+        <v>613421</v>
       </c>
       <c r="R35" t="n">
-        <v>7041618</v>
+        <v>7041692</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4142,7 +4143,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4152,7 +4153,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4189,10 +4190,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121255044</v>
+        <v>121255011</v>
       </c>
       <c r="B36" t="n">
-        <v>57351</v>
+        <v>90710</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4205,39 +4206,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613475</v>
+        <v>613415</v>
       </c>
       <c r="R36" t="n">
-        <v>7041662</v>
+        <v>7041708</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4264,17 +4260,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4301,10 +4292,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121255040</v>
+        <v>121255049</v>
       </c>
       <c r="B37" t="n">
-        <v>90709</v>
+        <v>91150</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4313,25 +4304,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4341,10 +4332,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613542</v>
+        <v>613523</v>
       </c>
       <c r="R37" t="n">
-        <v>7041619</v>
+        <v>7041640</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4403,10 +4394,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121255026</v>
+        <v>121255038</v>
       </c>
       <c r="B38" t="n">
-        <v>91149</v>
+        <v>90675</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4415,25 +4406,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4443,10 +4434,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>613371</v>
+        <v>613396</v>
       </c>
       <c r="R38" t="n">
-        <v>7041736</v>
+        <v>7041694</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4473,12 +4464,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4505,10 +4496,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121255056</v>
+        <v>121255023</v>
       </c>
       <c r="B39" t="n">
-        <v>98094</v>
+        <v>57367</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4517,30 +4508,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>150</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4549,10 +4541,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>613391</v>
+        <v>613442</v>
       </c>
       <c r="R39" t="n">
-        <v>7041785</v>
+        <v>7041756</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4579,12 +4571,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4611,10 +4603,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121255057</v>
+        <v>121255052</v>
       </c>
       <c r="B40" t="n">
-        <v>90723</v>
+        <v>98095</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4623,38 +4615,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>613523</v>
+        <v>613542</v>
       </c>
       <c r="R40" t="n">
-        <v>7041633</v>
+        <v>7041572</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4713,10 +4709,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121255014</v>
+        <v>121255029</v>
       </c>
       <c r="B41" t="n">
-        <v>90709</v>
+        <v>98095</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4725,38 +4721,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>613462</v>
+        <v>613510</v>
       </c>
       <c r="R41" t="n">
-        <v>7041669</v>
+        <v>7041675</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4815,10 +4815,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121255009</v>
+        <v>121255026</v>
       </c>
       <c r="B42" t="n">
-        <v>90709</v>
+        <v>91150</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4827,25 +4827,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>613396</v>
+        <v>613371</v>
       </c>
       <c r="R42" t="n">
-        <v>7041771</v>
+        <v>7041736</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255046</v>
+        <v>121255006</v>
       </c>
       <c r="B2" t="n">
-        <v>90730</v>
+        <v>74713</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613534</v>
+        <v>613519</v>
       </c>
       <c r="R2" t="n">
-        <v>7041558</v>
+        <v>7041683</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255037</v>
+        <v>121255048</v>
       </c>
       <c r="B3" t="n">
-        <v>90675</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613554</v>
+        <v>613373</v>
       </c>
       <c r="R3" t="n">
-        <v>7041628</v>
+        <v>7041694</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121255053</v>
+        <v>121255043</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>90713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,42 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613554</v>
+        <v>613421</v>
       </c>
       <c r="R4" t="n">
-        <v>7041573</v>
+        <v>7041692</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121255055</v>
+        <v>121255026</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>91153</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,38 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613400</v>
+        <v>613371</v>
       </c>
       <c r="R5" t="n">
-        <v>7041781</v>
+        <v>7041736</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1059,12 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121255056</v>
+        <v>121255054</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,7 +1123,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1135,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613391</v>
+        <v>613568</v>
       </c>
       <c r="R6" t="n">
-        <v>7041785</v>
+        <v>7041618</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1150,7 +1147,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1160,7 +1157,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1197,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121255006</v>
+        <v>121255023</v>
       </c>
       <c r="B7" t="n">
-        <v>74710</v>
+        <v>57370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1213,34 +1210,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613519</v>
+        <v>613442</v>
       </c>
       <c r="R7" t="n">
-        <v>7041683</v>
+        <v>7041756</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1299,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121255040</v>
+        <v>121255016</v>
       </c>
       <c r="B8" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613542</v>
+        <v>613505</v>
       </c>
       <c r="R8" t="n">
-        <v>7041619</v>
+        <v>7041675</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1369,12 +1371,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121255041</v>
+        <v>121255009</v>
       </c>
       <c r="B9" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613536</v>
+        <v>613396</v>
       </c>
       <c r="R9" t="n">
-        <v>7041639</v>
+        <v>7041771</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1471,12 +1473,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121255008</v>
+        <v>121255025</v>
       </c>
       <c r="B10" t="n">
-        <v>90675</v>
+        <v>91153</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1515,25 +1517,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613391</v>
+        <v>613463</v>
       </c>
       <c r="R10" t="n">
-        <v>7041765</v>
+        <v>7041737</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1605,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121255045</v>
+        <v>121255041</v>
       </c>
       <c r="B11" t="n">
-        <v>56563</v>
+        <v>90713</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1617,25 +1619,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1645,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613481</v>
+        <v>613536</v>
       </c>
       <c r="R11" t="n">
-        <v>7041555</v>
+        <v>7041639</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1707,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121255015</v>
+        <v>121255037</v>
       </c>
       <c r="B12" t="n">
-        <v>90710</v>
+        <v>90678</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1719,25 +1721,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613481</v>
+        <v>613554</v>
       </c>
       <c r="R12" t="n">
-        <v>7041676</v>
+        <v>7041628</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1777,12 +1779,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121255051</v>
+        <v>121255038</v>
       </c>
       <c r="B13" t="n">
-        <v>79685</v>
+        <v>90678</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1821,25 +1823,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1849,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613451</v>
+        <v>613396</v>
       </c>
       <c r="R13" t="n">
-        <v>7041510</v>
+        <v>7041694</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1911,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121255054</v>
+        <v>121255029</v>
       </c>
       <c r="B14" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1946,7 +1948,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1955,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613568</v>
+        <v>613510</v>
       </c>
       <c r="R14" t="n">
-        <v>7041618</v>
+        <v>7041675</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1970,7 +1972,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1980,17 +1982,17 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2017,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121255050</v>
+        <v>121255056</v>
       </c>
       <c r="B15" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2029,38 +2031,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613348</v>
+        <v>613391</v>
       </c>
       <c r="R15" t="n">
-        <v>7041806</v>
+        <v>7041785</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2101,7 +2107,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2120,10 +2125,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121255016</v>
+        <v>121255034</v>
       </c>
       <c r="B16" t="n">
-        <v>90710</v>
+        <v>78607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2136,21 +2141,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2160,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613505</v>
+        <v>613618</v>
       </c>
       <c r="R16" t="n">
-        <v>7041675</v>
+        <v>7041721</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2175,7 +2180,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2185,7 +2190,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2222,10 +2227,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121255031</v>
+        <v>121255039</v>
       </c>
       <c r="B17" t="n">
-        <v>90724</v>
+        <v>90678</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2234,25 +2239,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2262,10 +2267,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613377</v>
+        <v>613386</v>
       </c>
       <c r="R17" t="n">
-        <v>7041742</v>
+        <v>7041700</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2292,12 +2297,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2324,10 +2329,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121255048</v>
+        <v>121255031</v>
       </c>
       <c r="B18" t="n">
-        <v>57367</v>
+        <v>90727</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2340,39 +2345,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613373</v>
+        <v>613377</v>
       </c>
       <c r="R18" t="n">
-        <v>7041694</v>
+        <v>7041742</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2431,10 +2431,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121255025</v>
+        <v>121255015</v>
       </c>
       <c r="B19" t="n">
-        <v>91150</v>
+        <v>90713</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2443,25 +2443,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613463</v>
+        <v>613481</v>
       </c>
       <c r="R19" t="n">
-        <v>7041737</v>
+        <v>7041676</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121255039</v>
+        <v>121255014</v>
       </c>
       <c r="B20" t="n">
-        <v>90675</v>
+        <v>90713</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2545,25 +2545,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613386</v>
+        <v>613462</v>
       </c>
       <c r="R20" t="n">
-        <v>7041700</v>
+        <v>7041669</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,10 +2635,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121255014</v>
+        <v>121255032</v>
       </c>
       <c r="B21" t="n">
-        <v>90710</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613462</v>
+        <v>613446</v>
       </c>
       <c r="R21" t="n">
-        <v>7041669</v>
+        <v>7041752</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121255034</v>
+        <v>121255010</v>
       </c>
       <c r="B22" t="n">
-        <v>78604</v>
+        <v>90713</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2753,21 +2753,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613618</v>
+        <v>613391</v>
       </c>
       <c r="R22" t="n">
-        <v>7041721</v>
+        <v>7041765</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2839,10 +2839,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121255032</v>
+        <v>121255011</v>
       </c>
       <c r="B23" t="n">
-        <v>78604</v>
+        <v>90713</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2855,21 +2855,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613446</v>
+        <v>613415</v>
       </c>
       <c r="R23" t="n">
-        <v>7041752</v>
+        <v>7041708</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121255012</v>
+        <v>121255008</v>
       </c>
       <c r="B24" t="n">
-        <v>90710</v>
+        <v>90678</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2953,25 +2953,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613454</v>
+        <v>613391</v>
       </c>
       <c r="R24" t="n">
-        <v>7041671</v>
+        <v>7041765</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121255044</v>
+        <v>121255055</v>
       </c>
       <c r="B25" t="n">
-        <v>57351</v>
+        <v>98098</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3055,31 +3055,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3088,10 +3087,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613475</v>
+        <v>613400</v>
       </c>
       <c r="R25" t="n">
-        <v>7041662</v>
+        <v>7041781</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3124,11 +3123,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3155,10 +3149,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121255021</v>
+        <v>121255053</v>
       </c>
       <c r="B26" t="n">
-        <v>79714</v>
+        <v>98098</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3167,38 +3161,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>613468</v>
+        <v>613554</v>
       </c>
       <c r="R26" t="n">
-        <v>7041729</v>
+        <v>7041573</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3225,12 +3223,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3257,10 +3255,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121255009</v>
+        <v>121255044</v>
       </c>
       <c r="B27" t="n">
-        <v>90710</v>
+        <v>57354</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3273,34 +3271,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>613396</v>
+        <v>613475</v>
       </c>
       <c r="R27" t="n">
-        <v>7041771</v>
+        <v>7041662</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3327,12 +3330,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3359,10 +3367,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121255013</v>
+        <v>121255019</v>
       </c>
       <c r="B28" t="n">
-        <v>90710</v>
+        <v>57354</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3375,34 +3383,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613465</v>
+        <v>613528</v>
       </c>
       <c r="R28" t="n">
-        <v>7041678</v>
+        <v>7041701</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3435,6 +3448,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3461,10 +3479,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121255042</v>
+        <v>121255050</v>
       </c>
       <c r="B29" t="n">
-        <v>90710</v>
+        <v>79688</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3477,21 +3495,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3501,10 +3519,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613460</v>
+        <v>613348</v>
       </c>
       <c r="R29" t="n">
-        <v>7041672</v>
+        <v>7041806</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3545,6 +3563,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3563,10 +3582,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121255010</v>
+        <v>121255051</v>
       </c>
       <c r="B30" t="n">
-        <v>90710</v>
+        <v>79688</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3579,21 +3598,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3603,10 +3622,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613391</v>
+        <v>613451</v>
       </c>
       <c r="R30" t="n">
-        <v>7041765</v>
+        <v>7041510</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3633,12 +3652,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3665,10 +3684,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121255058</v>
+        <v>121255024</v>
       </c>
       <c r="B31" t="n">
-        <v>91366</v>
+        <v>57370</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3677,38 +3696,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>898</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613546</v>
+        <v>613541</v>
       </c>
       <c r="R31" t="n">
-        <v>7041646</v>
+        <v>7041685</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3735,12 +3759,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3767,10 +3791,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121255019</v>
+        <v>121255058</v>
       </c>
       <c r="B32" t="n">
-        <v>57351</v>
+        <v>91369</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3779,43 +3803,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613528</v>
+        <v>613546</v>
       </c>
       <c r="R32" t="n">
-        <v>7041701</v>
+        <v>7041646</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3842,17 +3861,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3879,10 +3893,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121255057</v>
+        <v>121255013</v>
       </c>
       <c r="B33" t="n">
-        <v>90724</v>
+        <v>90713</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3895,21 +3909,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3919,10 +3933,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>613523</v>
+        <v>613465</v>
       </c>
       <c r="R33" t="n">
-        <v>7041633</v>
+        <v>7041678</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3949,12 +3963,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3981,10 +3995,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121255024</v>
+        <v>121255042</v>
       </c>
       <c r="B34" t="n">
-        <v>57367</v>
+        <v>90713</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3997,39 +4011,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>613541</v>
+        <v>613460</v>
       </c>
       <c r="R34" t="n">
-        <v>7041685</v>
+        <v>7041672</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4056,12 +4065,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4088,10 +4097,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121255043</v>
+        <v>121255012</v>
       </c>
       <c r="B35" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4128,10 +4137,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>613421</v>
+        <v>613454</v>
       </c>
       <c r="R35" t="n">
-        <v>7041692</v>
+        <v>7041671</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4158,12 +4167,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4190,10 +4199,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121255011</v>
+        <v>121255046</v>
       </c>
       <c r="B36" t="n">
-        <v>90710</v>
+        <v>90733</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4206,21 +4215,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4230,10 +4239,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613415</v>
+        <v>613534</v>
       </c>
       <c r="R36" t="n">
-        <v>7041708</v>
+        <v>7041558</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4260,12 +4269,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4292,10 +4301,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121255049</v>
+        <v>121255052</v>
       </c>
       <c r="B37" t="n">
-        <v>91150</v>
+        <v>98098</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4308,34 +4317,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613523</v>
+        <v>613542</v>
       </c>
       <c r="R37" t="n">
-        <v>7041640</v>
+        <v>7041572</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4394,10 +4407,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121255038</v>
+        <v>121255045</v>
       </c>
       <c r="B38" t="n">
-        <v>90675</v>
+        <v>56566</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4410,21 +4423,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4434,10 +4447,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>613396</v>
+        <v>613481</v>
       </c>
       <c r="R38" t="n">
-        <v>7041694</v>
+        <v>7041555</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4496,10 +4509,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121255023</v>
+        <v>121255040</v>
       </c>
       <c r="B39" t="n">
-        <v>57367</v>
+        <v>90713</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4512,39 +4525,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>613442</v>
+        <v>613542</v>
       </c>
       <c r="R39" t="n">
-        <v>7041756</v>
+        <v>7041619</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4571,12 +4579,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4603,10 +4611,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121255052</v>
+        <v>121255057</v>
       </c>
       <c r="B40" t="n">
-        <v>98095</v>
+        <v>90727</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4615,42 +4623,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>613542</v>
+        <v>613523</v>
       </c>
       <c r="R40" t="n">
-        <v>7041572</v>
+        <v>7041633</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4709,10 +4713,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121255029</v>
+        <v>121255049</v>
       </c>
       <c r="B41" t="n">
-        <v>98095</v>
+        <v>91153</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4725,38 +4729,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>613510</v>
+        <v>613523</v>
       </c>
       <c r="R41" t="n">
-        <v>7041675</v>
+        <v>7041640</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4783,12 +4783,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4815,10 +4815,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121255026</v>
+        <v>121255021</v>
       </c>
       <c r="B42" t="n">
-        <v>91150</v>
+        <v>79717</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4827,25 +4827,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>613371</v>
+        <v>613468</v>
       </c>
       <c r="R42" t="n">
-        <v>7041736</v>
+        <v>7041729</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255006</v>
+        <v>121255009</v>
       </c>
       <c r="B2" t="n">
-        <v>74713</v>
+        <v>90713</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613519</v>
+        <v>613396</v>
       </c>
       <c r="R2" t="n">
-        <v>7041683</v>
+        <v>7041771</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255048</v>
+        <v>121255043</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>90713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613373</v>
+        <v>613421</v>
       </c>
       <c r="R3" t="n">
-        <v>7041694</v>
+        <v>7041692</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121255043</v>
+        <v>121255034</v>
       </c>
       <c r="B4" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613421</v>
+        <v>613618</v>
       </c>
       <c r="R4" t="n">
-        <v>7041692</v>
+        <v>7041721</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -939,7 +934,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -949,17 +944,17 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121255026</v>
+        <v>121255040</v>
       </c>
       <c r="B5" t="n">
-        <v>91153</v>
+        <v>90713</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613371</v>
+        <v>613542</v>
       </c>
       <c r="R5" t="n">
-        <v>7041736</v>
+        <v>7041619</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1056,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121255054</v>
+        <v>121255050</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,42 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613568</v>
+        <v>613348</v>
       </c>
       <c r="R6" t="n">
-        <v>7041618</v>
+        <v>7041806</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1147,7 +1138,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1157,7 +1148,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1176,6 +1167,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1194,7 +1186,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121255023</v>
+        <v>121255024</v>
       </c>
       <c r="B7" t="n">
         <v>57370</v>
@@ -1230,7 +1222,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1239,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613442</v>
+        <v>613541</v>
       </c>
       <c r="R7" t="n">
-        <v>7041756</v>
+        <v>7041685</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1301,7 +1293,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121255016</v>
+        <v>121255042</v>
       </c>
       <c r="B8" t="n">
         <v>90713</v>
@@ -1341,10 +1333,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613505</v>
+        <v>613460</v>
       </c>
       <c r="R8" t="n">
-        <v>7041675</v>
+        <v>7041672</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1371,12 +1363,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,10 +1395,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121255009</v>
+        <v>121255038</v>
       </c>
       <c r="B9" t="n">
-        <v>90713</v>
+        <v>90678</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,25 +1407,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1446,7 +1438,7 @@
         <v>613396</v>
       </c>
       <c r="R9" t="n">
-        <v>7041771</v>
+        <v>7041694</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1473,12 +1465,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,10 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121255025</v>
+        <v>121255023</v>
       </c>
       <c r="B10" t="n">
-        <v>91153</v>
+        <v>57370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,38 +1509,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613463</v>
+        <v>613442</v>
       </c>
       <c r="R10" t="n">
-        <v>7041737</v>
+        <v>7041756</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1607,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121255041</v>
+        <v>121255052</v>
       </c>
       <c r="B11" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,38 +1616,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613536</v>
+        <v>613542</v>
       </c>
       <c r="R11" t="n">
-        <v>7041639</v>
+        <v>7041572</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1709,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121255037</v>
+        <v>121255014</v>
       </c>
       <c r="B12" t="n">
-        <v>90678</v>
+        <v>90713</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1749,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613554</v>
+        <v>613462</v>
       </c>
       <c r="R12" t="n">
-        <v>7041628</v>
+        <v>7041669</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1779,12 +1780,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1811,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121255038</v>
+        <v>121255006</v>
       </c>
       <c r="B13" t="n">
-        <v>90678</v>
+        <v>74713</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613396</v>
+        <v>613519</v>
       </c>
       <c r="R13" t="n">
-        <v>7041694</v>
+        <v>7041683</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1881,12 +1882,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1913,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121255029</v>
+        <v>121255045</v>
       </c>
       <c r="B14" t="n">
-        <v>98098</v>
+        <v>56566</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,42 +1926,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613510</v>
+        <v>613481</v>
       </c>
       <c r="R14" t="n">
-        <v>7041675</v>
+        <v>7041555</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1987,12 +1984,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2019,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121255056</v>
+        <v>121255058</v>
       </c>
       <c r="B15" t="n">
-        <v>98098</v>
+        <v>91369</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2035,38 +2032,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613391</v>
+        <v>613546</v>
       </c>
       <c r="R15" t="n">
-        <v>7041785</v>
+        <v>7041646</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2125,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121255034</v>
+        <v>121255031</v>
       </c>
       <c r="B16" t="n">
-        <v>78607</v>
+        <v>90727</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2141,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2165,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613618</v>
+        <v>613377</v>
       </c>
       <c r="R16" t="n">
-        <v>7041721</v>
+        <v>7041742</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2180,7 +2173,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2190,7 +2183,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2227,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121255039</v>
+        <v>121255057</v>
       </c>
       <c r="B17" t="n">
-        <v>90678</v>
+        <v>90727</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2239,25 +2232,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2267,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613386</v>
+        <v>613523</v>
       </c>
       <c r="R17" t="n">
-        <v>7041700</v>
+        <v>7041633</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2329,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121255031</v>
+        <v>121255010</v>
       </c>
       <c r="B18" t="n">
-        <v>90727</v>
+        <v>90713</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2345,21 +2338,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2369,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613377</v>
+        <v>613391</v>
       </c>
       <c r="R18" t="n">
-        <v>7041742</v>
+        <v>7041765</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2431,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121255015</v>
+        <v>121255044</v>
       </c>
       <c r="B19" t="n">
-        <v>90713</v>
+        <v>57354</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2447,34 +2440,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613481</v>
+        <v>613475</v>
       </c>
       <c r="R19" t="n">
-        <v>7041676</v>
+        <v>7041662</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2501,12 +2499,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2533,7 +2536,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121255014</v>
+        <v>121255011</v>
       </c>
       <c r="B20" t="n">
         <v>90713</v>
@@ -2573,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613462</v>
+        <v>613415</v>
       </c>
       <c r="R20" t="n">
-        <v>7041669</v>
+        <v>7041708</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2737,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121255010</v>
+        <v>121255025</v>
       </c>
       <c r="B22" t="n">
-        <v>90713</v>
+        <v>91153</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2749,25 +2752,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2777,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613391</v>
+        <v>613463</v>
       </c>
       <c r="R22" t="n">
-        <v>7041765</v>
+        <v>7041737</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2839,7 +2842,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121255011</v>
+        <v>121255013</v>
       </c>
       <c r="B23" t="n">
         <v>90713</v>
@@ -2879,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613415</v>
+        <v>613465</v>
       </c>
       <c r="R23" t="n">
-        <v>7041708</v>
+        <v>7041678</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2941,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121255008</v>
+        <v>121255056</v>
       </c>
       <c r="B24" t="n">
-        <v>90678</v>
+        <v>98098</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2953,28 +2956,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
@@ -2984,7 +2991,7 @@
         <v>613391</v>
       </c>
       <c r="R24" t="n">
-        <v>7041765</v>
+        <v>7041785</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3011,12 +3018,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3043,10 +3050,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121255055</v>
+        <v>121255015</v>
       </c>
       <c r="B25" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3055,42 +3062,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613400</v>
+        <v>613481</v>
       </c>
       <c r="R25" t="n">
-        <v>7041781</v>
+        <v>7041676</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3117,12 +3120,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3149,10 +3152,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121255053</v>
+        <v>121255026</v>
       </c>
       <c r="B26" t="n">
-        <v>98098</v>
+        <v>91153</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3165,38 +3168,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>613554</v>
+        <v>613371</v>
       </c>
       <c r="R26" t="n">
-        <v>7041573</v>
+        <v>7041736</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3223,12 +3222,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3255,10 +3254,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121255044</v>
+        <v>121255049</v>
       </c>
       <c r="B27" t="n">
-        <v>57354</v>
+        <v>91153</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3267,43 +3266,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>613475</v>
+        <v>613523</v>
       </c>
       <c r="R27" t="n">
-        <v>7041662</v>
+        <v>7041640</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3336,11 +3330,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3367,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121255019</v>
+        <v>121255008</v>
       </c>
       <c r="B28" t="n">
-        <v>57354</v>
+        <v>90678</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3379,43 +3368,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613528</v>
+        <v>613391</v>
       </c>
       <c r="R28" t="n">
-        <v>7041701</v>
+        <v>7041765</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3448,11 +3432,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3479,10 +3458,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121255050</v>
+        <v>121255019</v>
       </c>
       <c r="B29" t="n">
-        <v>79688</v>
+        <v>57354</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3495,34 +3474,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613348</v>
+        <v>613528</v>
       </c>
       <c r="R29" t="n">
-        <v>7041806</v>
+        <v>7041701</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3549,12 +3533,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3563,7 +3552,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3582,10 +3570,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121255051</v>
+        <v>121255053</v>
       </c>
       <c r="B30" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3594,38 +3582,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613451</v>
+        <v>613554</v>
       </c>
       <c r="R30" t="n">
-        <v>7041510</v>
+        <v>7041573</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3684,10 +3676,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121255024</v>
+        <v>121255041</v>
       </c>
       <c r="B31" t="n">
-        <v>57370</v>
+        <v>90713</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3700,39 +3692,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613541</v>
+        <v>613536</v>
       </c>
       <c r="R31" t="n">
-        <v>7041685</v>
+        <v>7041639</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3759,12 +3746,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3791,10 +3778,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121255058</v>
+        <v>121255016</v>
       </c>
       <c r="B32" t="n">
-        <v>91369</v>
+        <v>90713</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3803,25 +3790,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3831,10 +3818,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613546</v>
+        <v>613505</v>
       </c>
       <c r="R32" t="n">
-        <v>7041646</v>
+        <v>7041675</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3861,12 +3848,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3893,7 +3880,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121255013</v>
+        <v>121255012</v>
       </c>
       <c r="B33" t="n">
         <v>90713</v>
@@ -3933,10 +3920,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>613465</v>
+        <v>613454</v>
       </c>
       <c r="R33" t="n">
-        <v>7041678</v>
+        <v>7041671</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3995,10 +3982,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121255042</v>
+        <v>121255054</v>
       </c>
       <c r="B34" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4007,38 +3994,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>613460</v>
+        <v>613568</v>
       </c>
       <c r="R34" t="n">
-        <v>7041672</v>
+        <v>7041618</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4050,7 +4041,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -4060,7 +4051,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4097,10 +4088,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121255012</v>
+        <v>121255021</v>
       </c>
       <c r="B35" t="n">
-        <v>90713</v>
+        <v>79717</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4109,25 +4100,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4137,10 +4128,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>613454</v>
+        <v>613468</v>
       </c>
       <c r="R35" t="n">
-        <v>7041671</v>
+        <v>7041729</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4199,10 +4190,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121255046</v>
+        <v>121255037</v>
       </c>
       <c r="B36" t="n">
-        <v>90733</v>
+        <v>90678</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4211,25 +4202,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4239,10 +4230,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613534</v>
+        <v>613554</v>
       </c>
       <c r="R36" t="n">
-        <v>7041558</v>
+        <v>7041628</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4301,7 +4292,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121255052</v>
+        <v>121255055</v>
       </c>
       <c r="B37" t="n">
         <v>98098</v>
@@ -4336,7 +4327,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4345,10 +4336,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613542</v>
+        <v>613400</v>
       </c>
       <c r="R37" t="n">
-        <v>7041572</v>
+        <v>7041781</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4407,10 +4398,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121255045</v>
+        <v>121255046</v>
       </c>
       <c r="B38" t="n">
-        <v>56566</v>
+        <v>90733</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4419,25 +4410,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4447,10 +4438,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>613481</v>
+        <v>613534</v>
       </c>
       <c r="R38" t="n">
-        <v>7041555</v>
+        <v>7041558</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4509,10 +4500,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121255040</v>
+        <v>121255029</v>
       </c>
       <c r="B39" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4521,38 +4512,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>613542</v>
+        <v>613510</v>
       </c>
       <c r="R39" t="n">
-        <v>7041619</v>
+        <v>7041675</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4579,12 +4574,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4611,10 +4606,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121255057</v>
+        <v>121255039</v>
       </c>
       <c r="B40" t="n">
-        <v>90727</v>
+        <v>90678</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4623,25 +4618,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4651,10 +4646,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>613523</v>
+        <v>613386</v>
       </c>
       <c r="R40" t="n">
-        <v>7041633</v>
+        <v>7041700</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4713,10 +4708,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121255049</v>
+        <v>121255051</v>
       </c>
       <c r="B41" t="n">
-        <v>91153</v>
+        <v>79688</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4725,25 +4720,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4753,10 +4748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>613523</v>
+        <v>613451</v>
       </c>
       <c r="R41" t="n">
-        <v>7041640</v>
+        <v>7041510</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4815,10 +4810,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121255021</v>
+        <v>121255048</v>
       </c>
       <c r="B42" t="n">
-        <v>79717</v>
+        <v>57370</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4827,38 +4822,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>613468</v>
+        <v>613373</v>
       </c>
       <c r="R42" t="n">
-        <v>7041729</v>
+        <v>7041694</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121255014</v>
+        <v>121255006</v>
       </c>
       <c r="B12" t="n">
-        <v>90713</v>
+        <v>74713</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613462</v>
+        <v>613519</v>
       </c>
       <c r="R12" t="n">
-        <v>7041669</v>
+        <v>7041683</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121255006</v>
+        <v>121255014</v>
       </c>
       <c r="B13" t="n">
-        <v>74713</v>
+        <v>90713</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613519</v>
+        <v>613462</v>
       </c>
       <c r="R13" t="n">
-        <v>7041683</v>
+        <v>7041669</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121255006</v>
+        <v>121255014</v>
       </c>
       <c r="B12" t="n">
-        <v>74713</v>
+        <v>90713</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613519</v>
+        <v>613462</v>
       </c>
       <c r="R12" t="n">
-        <v>7041683</v>
+        <v>7041669</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121255014</v>
+        <v>121255006</v>
       </c>
       <c r="B13" t="n">
-        <v>90713</v>
+        <v>74713</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613462</v>
+        <v>613519</v>
       </c>
       <c r="R13" t="n">
-        <v>7041669</v>
+        <v>7041683</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -4606,10 +4606,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121255039</v>
+        <v>121255051</v>
       </c>
       <c r="B40" t="n">
-        <v>90678</v>
+        <v>79688</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4618,25 +4618,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>613386</v>
+        <v>613451</v>
       </c>
       <c r="R40" t="n">
-        <v>7041700</v>
+        <v>7041510</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4708,10 +4708,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121255051</v>
+        <v>121255039</v>
       </c>
       <c r="B41" t="n">
-        <v>79688</v>
+        <v>90678</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4720,25 +4720,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4748,10 +4748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>613451</v>
+        <v>613386</v>
       </c>
       <c r="R41" t="n">
-        <v>7041510</v>
+        <v>7041700</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255009</v>
+        <v>121255049</v>
       </c>
       <c r="B2" t="n">
-        <v>90713</v>
+        <v>91159</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613396</v>
+        <v>613523</v>
       </c>
       <c r="R2" t="n">
-        <v>7041771</v>
+        <v>7041640</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255043</v>
+        <v>121255009</v>
       </c>
       <c r="B3" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613421</v>
+        <v>613396</v>
       </c>
       <c r="R3" t="n">
-        <v>7041692</v>
+        <v>7041771</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121255034</v>
+        <v>121255055</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613618</v>
+        <v>613400</v>
       </c>
       <c r="R4" t="n">
-        <v>7041721</v>
+        <v>7041781</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -934,7 +938,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -944,17 +948,17 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121255040</v>
+        <v>121255010</v>
       </c>
       <c r="B5" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613542</v>
+        <v>613391</v>
       </c>
       <c r="R5" t="n">
-        <v>7041619</v>
+        <v>7041765</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1051,12 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121255050</v>
+        <v>121255052</v>
       </c>
       <c r="B6" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1099,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613348</v>
+        <v>613542</v>
       </c>
       <c r="R6" t="n">
-        <v>7041806</v>
+        <v>7041572</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1167,7 +1175,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1186,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121255024</v>
+        <v>121255026</v>
       </c>
       <c r="B7" t="n">
-        <v>57370</v>
+        <v>91159</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1198,43 +1205,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613541</v>
+        <v>613371</v>
       </c>
       <c r="R7" t="n">
-        <v>7041685</v>
+        <v>7041736</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1293,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121255042</v>
+        <v>121255016</v>
       </c>
       <c r="B8" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613460</v>
+        <v>613505</v>
       </c>
       <c r="R8" t="n">
-        <v>7041672</v>
+        <v>7041675</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1363,12 +1365,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1395,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121255038</v>
+        <v>121255057</v>
       </c>
       <c r="B9" t="n">
-        <v>90678</v>
+        <v>90733</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1407,25 +1409,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1435,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613396</v>
+        <v>613523</v>
       </c>
       <c r="R9" t="n">
-        <v>7041694</v>
+        <v>7041633</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1497,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121255023</v>
+        <v>121255039</v>
       </c>
       <c r="B10" t="n">
-        <v>57370</v>
+        <v>90684</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1509,43 +1511,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613442</v>
+        <v>613386</v>
       </c>
       <c r="R10" t="n">
-        <v>7041756</v>
+        <v>7041700</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1572,12 +1569,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1604,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121255052</v>
+        <v>121255043</v>
       </c>
       <c r="B11" t="n">
-        <v>98098</v>
+        <v>90719</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1616,42 +1613,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613542</v>
+        <v>613421</v>
       </c>
       <c r="R11" t="n">
-        <v>7041572</v>
+        <v>7041692</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1710,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121255014</v>
+        <v>121255031</v>
       </c>
       <c r="B12" t="n">
-        <v>90713</v>
+        <v>90733</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1719,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613462</v>
+        <v>613377</v>
       </c>
       <c r="R12" t="n">
-        <v>7041669</v>
+        <v>7041742</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1812,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121255006</v>
+        <v>121255038</v>
       </c>
       <c r="B13" t="n">
-        <v>74713</v>
+        <v>90684</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1817,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613519</v>
+        <v>613396</v>
       </c>
       <c r="R13" t="n">
-        <v>7041683</v>
+        <v>7041694</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1882,12 +1875,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121255045</v>
+        <v>121255032</v>
       </c>
       <c r="B14" t="n">
-        <v>56566</v>
+        <v>78608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1919,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1947,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613481</v>
+        <v>613446</v>
       </c>
       <c r="R14" t="n">
-        <v>7041555</v>
+        <v>7041752</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1984,12 +1977,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,10 +2009,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121255058</v>
+        <v>121255021</v>
       </c>
       <c r="B15" t="n">
-        <v>91369</v>
+        <v>79718</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2021,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>898</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2049,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613546</v>
+        <v>613468</v>
       </c>
       <c r="R15" t="n">
-        <v>7041646</v>
+        <v>7041729</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2086,12 +2079,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2118,10 +2111,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121255031</v>
+        <v>121255011</v>
       </c>
       <c r="B16" t="n">
-        <v>90727</v>
+        <v>90719</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,21 +2127,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2151,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613377</v>
+        <v>613415</v>
       </c>
       <c r="R16" t="n">
-        <v>7041742</v>
+        <v>7041708</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2220,10 +2213,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121255057</v>
+        <v>121255037</v>
       </c>
       <c r="B17" t="n">
-        <v>90727</v>
+        <v>90684</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,25 +2225,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613523</v>
+        <v>613554</v>
       </c>
       <c r="R17" t="n">
-        <v>7041633</v>
+        <v>7041628</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2322,10 +2315,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121255010</v>
+        <v>121255048</v>
       </c>
       <c r="B18" t="n">
-        <v>90713</v>
+        <v>57371</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,34 +2331,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613391</v>
+        <v>613373</v>
       </c>
       <c r="R18" t="n">
-        <v>7041765</v>
+        <v>7041694</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2392,12 +2390,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2424,10 +2422,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121255044</v>
+        <v>121255056</v>
       </c>
       <c r="B19" t="n">
-        <v>57354</v>
+        <v>98104</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2436,31 +2434,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2469,10 +2466,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613475</v>
+        <v>613391</v>
       </c>
       <c r="R19" t="n">
-        <v>7041662</v>
+        <v>7041785</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2505,11 +2502,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2536,10 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121255011</v>
+        <v>121255044</v>
       </c>
       <c r="B20" t="n">
-        <v>90713</v>
+        <v>57355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,34 +2544,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613415</v>
+        <v>613475</v>
       </c>
       <c r="R20" t="n">
-        <v>7041708</v>
+        <v>7041662</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2606,12 +2603,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2638,10 +2640,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121255032</v>
+        <v>121255013</v>
       </c>
       <c r="B21" t="n">
-        <v>78607</v>
+        <v>90719</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,21 +2656,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2680,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613446</v>
+        <v>613465</v>
       </c>
       <c r="R21" t="n">
-        <v>7041752</v>
+        <v>7041678</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2743,7 +2745,7 @@
         <v>121255025</v>
       </c>
       <c r="B22" t="n">
-        <v>91153</v>
+        <v>91159</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2842,10 +2844,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121255013</v>
+        <v>121255034</v>
       </c>
       <c r="B23" t="n">
-        <v>90713</v>
+        <v>78608</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,21 +2860,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2884,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613465</v>
+        <v>613618</v>
       </c>
       <c r="R23" t="n">
-        <v>7041678</v>
+        <v>7041721</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2897,7 +2899,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2907,7 +2909,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2944,10 +2946,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121255056</v>
+        <v>121255019</v>
       </c>
       <c r="B24" t="n">
-        <v>98098</v>
+        <v>57355</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,30 +2958,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>150</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2988,10 +2991,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613391</v>
+        <v>613528</v>
       </c>
       <c r="R24" t="n">
-        <v>7041785</v>
+        <v>7041701</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3018,12 +3021,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3050,10 +3058,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121255015</v>
+        <v>121255042</v>
       </c>
       <c r="B25" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3090,10 +3098,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613481</v>
+        <v>613460</v>
       </c>
       <c r="R25" t="n">
-        <v>7041676</v>
+        <v>7041672</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3120,12 +3128,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3152,10 +3160,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121255026</v>
+        <v>121255014</v>
       </c>
       <c r="B26" t="n">
-        <v>91153</v>
+        <v>90719</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,25 +3172,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3192,10 +3200,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>613371</v>
+        <v>613462</v>
       </c>
       <c r="R26" t="n">
-        <v>7041736</v>
+        <v>7041669</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3254,10 +3262,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121255049</v>
+        <v>121255015</v>
       </c>
       <c r="B27" t="n">
-        <v>91153</v>
+        <v>90719</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,25 +3274,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3294,10 +3302,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>613523</v>
+        <v>613481</v>
       </c>
       <c r="R27" t="n">
-        <v>7041640</v>
+        <v>7041676</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3324,12 +3332,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3356,10 +3364,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121255008</v>
+        <v>121255045</v>
       </c>
       <c r="B28" t="n">
-        <v>90678</v>
+        <v>56567</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3372,21 +3380,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3396,10 +3404,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613391</v>
+        <v>613481</v>
       </c>
       <c r="R28" t="n">
-        <v>7041765</v>
+        <v>7041555</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3426,12 +3434,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3458,10 +3466,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121255019</v>
+        <v>121255029</v>
       </c>
       <c r="B29" t="n">
-        <v>57354</v>
+        <v>98104</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3470,31 +3478,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3503,10 +3510,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613528</v>
+        <v>613510</v>
       </c>
       <c r="R29" t="n">
-        <v>7041701</v>
+        <v>7041675</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3539,11 +3546,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3570,10 +3572,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121255053</v>
+        <v>121255040</v>
       </c>
       <c r="B30" t="n">
-        <v>98098</v>
+        <v>90719</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3582,42 +3584,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613554</v>
+        <v>613542</v>
       </c>
       <c r="R30" t="n">
-        <v>7041573</v>
+        <v>7041619</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3676,10 +3674,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121255041</v>
+        <v>121255008</v>
       </c>
       <c r="B31" t="n">
-        <v>90713</v>
+        <v>90684</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3688,25 +3686,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3716,10 +3714,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613536</v>
+        <v>613391</v>
       </c>
       <c r="R31" t="n">
-        <v>7041639</v>
+        <v>7041765</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3746,12 +3744,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3778,10 +3776,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121255016</v>
+        <v>121255053</v>
       </c>
       <c r="B32" t="n">
-        <v>90713</v>
+        <v>98104</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3790,38 +3788,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613505</v>
+        <v>613554</v>
       </c>
       <c r="R32" t="n">
-        <v>7041675</v>
+        <v>7041573</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3848,12 +3850,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3880,10 +3882,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121255012</v>
+        <v>121255054</v>
       </c>
       <c r="B33" t="n">
-        <v>90713</v>
+        <v>98104</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3892,38 +3894,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>613454</v>
+        <v>613568</v>
       </c>
       <c r="R33" t="n">
-        <v>7041671</v>
+        <v>7041618</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3935,7 +3941,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3945,17 +3951,17 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3982,10 +3988,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121255054</v>
+        <v>121255023</v>
       </c>
       <c r="B34" t="n">
-        <v>98098</v>
+        <v>57371</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3994,30 +4000,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4026,10 +4033,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>613568</v>
+        <v>613442</v>
       </c>
       <c r="R34" t="n">
-        <v>7041618</v>
+        <v>7041756</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4041,7 +4048,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -4051,17 +4058,17 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4088,10 +4095,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121255021</v>
+        <v>121255024</v>
       </c>
       <c r="B35" t="n">
-        <v>79717</v>
+        <v>57371</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4100,38 +4107,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>613468</v>
+        <v>613541</v>
       </c>
       <c r="R35" t="n">
-        <v>7041729</v>
+        <v>7041685</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4190,10 +4202,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121255037</v>
+        <v>121255006</v>
       </c>
       <c r="B36" t="n">
-        <v>90678</v>
+        <v>74714</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4202,25 +4214,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4230,10 +4242,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613554</v>
+        <v>613519</v>
       </c>
       <c r="R36" t="n">
-        <v>7041628</v>
+        <v>7041683</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4260,12 +4272,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4292,10 +4304,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121255055</v>
+        <v>121255051</v>
       </c>
       <c r="B37" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4304,42 +4316,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613400</v>
+        <v>613451</v>
       </c>
       <c r="R37" t="n">
-        <v>7041781</v>
+        <v>7041510</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4401,7 +4409,7 @@
         <v>121255046</v>
       </c>
       <c r="B38" t="n">
-        <v>90733</v>
+        <v>90739</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4500,10 +4508,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121255029</v>
+        <v>121255012</v>
       </c>
       <c r="B39" t="n">
-        <v>98098</v>
+        <v>90719</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4512,42 +4520,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>613510</v>
+        <v>613454</v>
       </c>
       <c r="R39" t="n">
-        <v>7041675</v>
+        <v>7041671</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4606,10 +4610,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121255051</v>
+        <v>121255041</v>
       </c>
       <c r="B40" t="n">
-        <v>79688</v>
+        <v>90719</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4622,21 +4626,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4646,10 +4650,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>613451</v>
+        <v>613536</v>
       </c>
       <c r="R40" t="n">
-        <v>7041510</v>
+        <v>7041639</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4708,10 +4712,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121255039</v>
+        <v>121255050</v>
       </c>
       <c r="B41" t="n">
-        <v>90678</v>
+        <v>79689</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4720,25 +4724,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4748,10 +4752,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>613386</v>
+        <v>613348</v>
       </c>
       <c r="R41" t="n">
-        <v>7041700</v>
+        <v>7041806</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4792,6 +4796,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4810,10 +4815,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121255048</v>
+        <v>121255058</v>
       </c>
       <c r="B42" t="n">
-        <v>57370</v>
+        <v>91375</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4822,43 +4827,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>898</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>613373</v>
+        <v>613546</v>
       </c>
       <c r="R42" t="n">
-        <v>7041694</v>
+        <v>7041646</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -2946,10 +2946,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121255019</v>
+        <v>121255042</v>
       </c>
       <c r="B24" t="n">
-        <v>57355</v>
+        <v>90719</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2962,39 +2962,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613528</v>
+        <v>613460</v>
       </c>
       <c r="R24" t="n">
-        <v>7041701</v>
+        <v>7041672</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3021,17 +3016,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3058,7 +3048,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121255042</v>
+        <v>121255014</v>
       </c>
       <c r="B25" t="n">
         <v>90719</v>
@@ -3098,10 +3088,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613460</v>
+        <v>613462</v>
       </c>
       <c r="R25" t="n">
-        <v>7041672</v>
+        <v>7041669</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3128,12 +3118,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3160,7 +3150,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121255014</v>
+        <v>121255015</v>
       </c>
       <c r="B26" t="n">
         <v>90719</v>
@@ -3200,10 +3190,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>613462</v>
+        <v>613481</v>
       </c>
       <c r="R26" t="n">
-        <v>7041669</v>
+        <v>7041676</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3262,10 +3252,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121255015</v>
+        <v>121255019</v>
       </c>
       <c r="B27" t="n">
-        <v>90719</v>
+        <v>57355</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3278,34 +3268,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>613481</v>
+        <v>613528</v>
       </c>
       <c r="R27" t="n">
-        <v>7041676</v>
+        <v>7041701</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3338,6 +3333,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3572,10 +3572,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121255040</v>
+        <v>121255008</v>
       </c>
       <c r="B30" t="n">
-        <v>90719</v>
+        <v>90684</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3584,25 +3584,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613542</v>
+        <v>613391</v>
       </c>
       <c r="R30" t="n">
-        <v>7041619</v>
+        <v>7041765</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3642,12 +3642,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3674,10 +3674,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121255008</v>
+        <v>121255040</v>
       </c>
       <c r="B31" t="n">
-        <v>90684</v>
+        <v>90719</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3686,25 +3686,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613391</v>
+        <v>613542</v>
       </c>
       <c r="R31" t="n">
-        <v>7041765</v>
+        <v>7041619</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3744,12 +3744,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255049</v>
+        <v>121255057</v>
       </c>
       <c r="B2" t="n">
-        <v>91159</v>
+        <v>90734</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,7 +718,7 @@
         <v>613523</v>
       </c>
       <c r="R2" t="n">
-        <v>7041640</v>
+        <v>7041633</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255009</v>
+        <v>121255031</v>
       </c>
       <c r="B3" t="n">
-        <v>90719</v>
+        <v>90734</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613396</v>
+        <v>613377</v>
       </c>
       <c r="R3" t="n">
-        <v>7041771</v>
+        <v>7041742</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121255055</v>
+        <v>121255023</v>
       </c>
       <c r="B4" t="n">
-        <v>98104</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,30 +891,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -923,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613400</v>
+        <v>613442</v>
       </c>
       <c r="R4" t="n">
-        <v>7041781</v>
+        <v>7041756</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -953,12 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121255010</v>
+        <v>121255049</v>
       </c>
       <c r="B5" t="n">
-        <v>90719</v>
+        <v>91160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613391</v>
+        <v>613523</v>
       </c>
       <c r="R5" t="n">
-        <v>7041765</v>
+        <v>7041640</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1055,12 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121255052</v>
+        <v>121255006</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>74715</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,42 +1100,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613542</v>
+        <v>613519</v>
       </c>
       <c r="R6" t="n">
-        <v>7041572</v>
+        <v>7041683</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1161,12 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121255026</v>
+        <v>121255046</v>
       </c>
       <c r="B7" t="n">
-        <v>91159</v>
+        <v>90740</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613371</v>
+        <v>613534</v>
       </c>
       <c r="R7" t="n">
-        <v>7041736</v>
+        <v>7041558</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1263,12 +1260,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121255016</v>
+        <v>121255041</v>
       </c>
       <c r="B8" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613505</v>
+        <v>613536</v>
       </c>
       <c r="R8" t="n">
-        <v>7041675</v>
+        <v>7041639</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1365,12 +1362,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121255057</v>
+        <v>121255029</v>
       </c>
       <c r="B9" t="n">
-        <v>90733</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,38 +1406,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613523</v>
+        <v>613510</v>
       </c>
       <c r="R9" t="n">
-        <v>7041633</v>
+        <v>7041675</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1467,12 +1468,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121255039</v>
+        <v>121255021</v>
       </c>
       <c r="B10" t="n">
-        <v>90684</v>
+        <v>79719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1515,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1539,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613386</v>
+        <v>613468</v>
       </c>
       <c r="R10" t="n">
-        <v>7041700</v>
+        <v>7041729</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1569,12 +1570,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121255043</v>
+        <v>121255009</v>
       </c>
       <c r="B11" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613421</v>
+        <v>613396</v>
       </c>
       <c r="R11" t="n">
-        <v>7041692</v>
+        <v>7041771</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1671,12 +1672,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121255031</v>
+        <v>121255054</v>
       </c>
       <c r="B12" t="n">
-        <v>90733</v>
+        <v>98105</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1715,38 +1716,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613377</v>
+        <v>613568</v>
       </c>
       <c r="R12" t="n">
-        <v>7041742</v>
+        <v>7041618</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1758,7 +1763,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1768,17 +1773,17 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121255038</v>
+        <v>121255025</v>
       </c>
       <c r="B13" t="n">
-        <v>90684</v>
+        <v>91160</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1817,25 +1822,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1845,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613396</v>
+        <v>613463</v>
       </c>
       <c r="R13" t="n">
-        <v>7041694</v>
+        <v>7041737</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1875,12 +1880,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1907,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121255032</v>
+        <v>121255050</v>
       </c>
       <c r="B14" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1923,21 +1928,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1947,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613446</v>
+        <v>613348</v>
       </c>
       <c r="R14" t="n">
-        <v>7041752</v>
+        <v>7041806</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1977,12 +1982,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,6 +1996,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2009,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121255021</v>
+        <v>121255055</v>
       </c>
       <c r="B15" t="n">
-        <v>79718</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2021,38 +2027,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613468</v>
+        <v>613400</v>
       </c>
       <c r="R15" t="n">
-        <v>7041729</v>
+        <v>7041781</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2079,12 +2089,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121255011</v>
+        <v>121255026</v>
       </c>
       <c r="B16" t="n">
-        <v>90719</v>
+        <v>91160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2123,25 +2133,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2151,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613415</v>
+        <v>613371</v>
       </c>
       <c r="R16" t="n">
-        <v>7041708</v>
+        <v>7041736</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2213,10 +2223,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121255037</v>
+        <v>121255034</v>
       </c>
       <c r="B17" t="n">
-        <v>90684</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2225,25 +2235,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2253,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613554</v>
+        <v>613618</v>
       </c>
       <c r="R17" t="n">
-        <v>7041628</v>
+        <v>7041721</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2268,7 +2278,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2278,17 +2288,17 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2315,10 +2325,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121255048</v>
+        <v>121255032</v>
       </c>
       <c r="B18" t="n">
-        <v>57371</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2331,39 +2341,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613373</v>
+        <v>613446</v>
       </c>
       <c r="R18" t="n">
-        <v>7041694</v>
+        <v>7041752</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2390,12 +2395,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2422,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121255056</v>
+        <v>121255016</v>
       </c>
       <c r="B19" t="n">
-        <v>98104</v>
+        <v>90720</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,42 +2439,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613391</v>
+        <v>613505</v>
       </c>
       <c r="R19" t="n">
-        <v>7041785</v>
+        <v>7041675</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2496,12 +2497,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2528,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121255044</v>
+        <v>121255024</v>
       </c>
       <c r="B20" t="n">
-        <v>57355</v>
+        <v>57372</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2544,16 +2545,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2564,7 +2565,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2573,10 +2574,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613475</v>
+        <v>613541</v>
       </c>
       <c r="R20" t="n">
-        <v>7041662</v>
+        <v>7041685</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2603,17 +2604,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2640,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121255013</v>
+        <v>121255051</v>
       </c>
       <c r="B21" t="n">
-        <v>90719</v>
+        <v>79690</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2656,21 +2652,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2680,10 +2676,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613465</v>
+        <v>613451</v>
       </c>
       <c r="R21" t="n">
-        <v>7041678</v>
+        <v>7041510</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2710,12 +2706,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2742,10 +2738,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121255025</v>
+        <v>121255019</v>
       </c>
       <c r="B22" t="n">
-        <v>91159</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2754,38 +2750,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613463</v>
+        <v>613528</v>
       </c>
       <c r="R22" t="n">
-        <v>7041737</v>
+        <v>7041701</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2818,6 +2819,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2844,10 +2850,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121255034</v>
+        <v>121255045</v>
       </c>
       <c r="B23" t="n">
-        <v>78608</v>
+        <v>56568</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2856,25 +2862,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2884,10 +2890,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613618</v>
+        <v>613481</v>
       </c>
       <c r="R23" t="n">
-        <v>7041721</v>
+        <v>7041555</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2899,7 +2905,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2909,17 +2915,17 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2946,10 +2952,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121255042</v>
+        <v>121255053</v>
       </c>
       <c r="B24" t="n">
-        <v>90719</v>
+        <v>98105</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2958,38 +2964,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613460</v>
+        <v>613554</v>
       </c>
       <c r="R24" t="n">
-        <v>7041672</v>
+        <v>7041573</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3048,10 +3058,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121255014</v>
+        <v>121255040</v>
       </c>
       <c r="B25" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3088,10 +3098,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613462</v>
+        <v>613542</v>
       </c>
       <c r="R25" t="n">
-        <v>7041669</v>
+        <v>7041619</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3118,12 +3128,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3150,10 +3160,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121255015</v>
+        <v>121255008</v>
       </c>
       <c r="B26" t="n">
-        <v>90719</v>
+        <v>90685</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3162,25 +3172,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3190,10 +3200,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>613481</v>
+        <v>613391</v>
       </c>
       <c r="R26" t="n">
-        <v>7041676</v>
+        <v>7041765</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3252,10 +3262,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121255019</v>
+        <v>121255014</v>
       </c>
       <c r="B27" t="n">
-        <v>57355</v>
+        <v>90720</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3268,39 +3278,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>613528</v>
+        <v>613462</v>
       </c>
       <c r="R27" t="n">
-        <v>7041701</v>
+        <v>7041669</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3333,11 +3338,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3364,10 +3364,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121255045</v>
+        <v>121255052</v>
       </c>
       <c r="B28" t="n">
-        <v>56567</v>
+        <v>98105</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3376,38 +3376,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613481</v>
+        <v>613542</v>
       </c>
       <c r="R28" t="n">
-        <v>7041555</v>
+        <v>7041572</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3466,10 +3470,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121255029</v>
+        <v>121255010</v>
       </c>
       <c r="B29" t="n">
-        <v>98104</v>
+        <v>90720</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3478,42 +3482,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613510</v>
+        <v>613391</v>
       </c>
       <c r="R29" t="n">
-        <v>7041675</v>
+        <v>7041765</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121255008</v>
+        <v>121255038</v>
       </c>
       <c r="B30" t="n">
-        <v>90684</v>
+        <v>90685</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613391</v>
+        <v>613396</v>
       </c>
       <c r="R30" t="n">
-        <v>7041765</v>
+        <v>7041694</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3642,12 +3642,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3674,10 +3674,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121255040</v>
+        <v>121255039</v>
       </c>
       <c r="B31" t="n">
-        <v>90719</v>
+        <v>90685</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3686,25 +3686,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613542</v>
+        <v>613386</v>
       </c>
       <c r="R31" t="n">
-        <v>7041619</v>
+        <v>7041700</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121255053</v>
+        <v>121255012</v>
       </c>
       <c r="B32" t="n">
-        <v>98104</v>
+        <v>90720</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3788,42 +3788,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613554</v>
+        <v>613454</v>
       </c>
       <c r="R32" t="n">
-        <v>7041573</v>
+        <v>7041671</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3850,12 +3846,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3882,10 +3878,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121255054</v>
+        <v>121255043</v>
       </c>
       <c r="B33" t="n">
-        <v>98104</v>
+        <v>90720</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3894,42 +3890,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>613568</v>
+        <v>613421</v>
       </c>
       <c r="R33" t="n">
-        <v>7041618</v>
+        <v>7041692</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3941,7 +3933,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3951,7 +3943,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3988,10 +3980,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121255023</v>
+        <v>121255013</v>
       </c>
       <c r="B34" t="n">
-        <v>57371</v>
+        <v>90720</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4004,39 +3996,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>613442</v>
+        <v>613465</v>
       </c>
       <c r="R34" t="n">
-        <v>7041756</v>
+        <v>7041678</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4095,10 +4082,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121255024</v>
+        <v>121255044</v>
       </c>
       <c r="B35" t="n">
-        <v>57371</v>
+        <v>57356</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4111,16 +4098,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4131,7 +4118,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4140,10 +4127,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>613541</v>
+        <v>613475</v>
       </c>
       <c r="R35" t="n">
-        <v>7041685</v>
+        <v>7041662</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4170,12 +4157,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4202,10 +4194,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121255006</v>
+        <v>121255042</v>
       </c>
       <c r="B36" t="n">
-        <v>74714</v>
+        <v>90720</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4218,21 +4210,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4242,10 +4234,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613519</v>
+        <v>613460</v>
       </c>
       <c r="R36" t="n">
-        <v>7041683</v>
+        <v>7041672</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4272,12 +4264,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4304,10 +4296,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121255051</v>
+        <v>121255056</v>
       </c>
       <c r="B37" t="n">
-        <v>79689</v>
+        <v>98105</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4316,38 +4308,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613451</v>
+        <v>613391</v>
       </c>
       <c r="R37" t="n">
-        <v>7041510</v>
+        <v>7041785</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4406,10 +4402,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121255046</v>
+        <v>121255011</v>
       </c>
       <c r="B38" t="n">
-        <v>90739</v>
+        <v>90720</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4422,21 +4418,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4446,10 +4442,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>613534</v>
+        <v>613415</v>
       </c>
       <c r="R38" t="n">
-        <v>7041558</v>
+        <v>7041708</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4476,12 +4472,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4508,10 +4504,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121255012</v>
+        <v>121255015</v>
       </c>
       <c r="B39" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4548,10 +4544,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>613454</v>
+        <v>613481</v>
       </c>
       <c r="R39" t="n">
-        <v>7041671</v>
+        <v>7041676</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4610,10 +4606,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121255041</v>
+        <v>121255037</v>
       </c>
       <c r="B40" t="n">
-        <v>90719</v>
+        <v>90685</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4622,25 +4618,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4650,10 +4646,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>613536</v>
+        <v>613554</v>
       </c>
       <c r="R40" t="n">
-        <v>7041639</v>
+        <v>7041628</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4712,10 +4708,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121255050</v>
+        <v>121255048</v>
       </c>
       <c r="B41" t="n">
-        <v>79689</v>
+        <v>57372</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4728,34 +4724,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>613348</v>
+        <v>613373</v>
       </c>
       <c r="R41" t="n">
-        <v>7041806</v>
+        <v>7041694</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4796,7 +4797,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>121255058</v>
       </c>
       <c r="B42" t="n">
-        <v>91375</v>
+        <v>91376</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255057</v>
+        <v>121255053</v>
       </c>
       <c r="B2" t="n">
-        <v>90734</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613523</v>
+        <v>613554</v>
       </c>
       <c r="R2" t="n">
-        <v>7041633</v>
+        <v>7041573</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255031</v>
+        <v>121255011</v>
       </c>
       <c r="B3" t="n">
-        <v>90734</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613377</v>
+        <v>613415</v>
       </c>
       <c r="R3" t="n">
-        <v>7041742</v>
+        <v>7041708</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121255023</v>
+        <v>121255043</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +899,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613442</v>
+        <v>613421</v>
       </c>
       <c r="R4" t="n">
-        <v>7041756</v>
+        <v>7041692</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -954,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121255049</v>
+        <v>121255008</v>
       </c>
       <c r="B5" t="n">
-        <v>91160</v>
+        <v>90685</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +997,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613523</v>
+        <v>613391</v>
       </c>
       <c r="R5" t="n">
-        <v>7041640</v>
+        <v>7041765</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1056,12 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121255006</v>
+        <v>121255009</v>
       </c>
       <c r="B6" t="n">
-        <v>74715</v>
+        <v>90720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613519</v>
+        <v>613396</v>
       </c>
       <c r="R6" t="n">
-        <v>7041683</v>
+        <v>7041771</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1190,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121255046</v>
+        <v>121255019</v>
       </c>
       <c r="B7" t="n">
-        <v>90740</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,34 +1205,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613534</v>
+        <v>613528</v>
       </c>
       <c r="R7" t="n">
-        <v>7041558</v>
+        <v>7041701</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1260,12 +1264,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121255041</v>
+        <v>121255034</v>
       </c>
       <c r="B8" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613536</v>
+        <v>613618</v>
       </c>
       <c r="R8" t="n">
-        <v>7041639</v>
+        <v>7041721</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1347,7 +1356,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1357,17 +1366,17 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121255029</v>
+        <v>121255014</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,42 +1415,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613510</v>
+        <v>613462</v>
       </c>
       <c r="R9" t="n">
-        <v>7041675</v>
+        <v>7041669</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121255021</v>
+        <v>121255057</v>
       </c>
       <c r="B10" t="n">
-        <v>79719</v>
+        <v>90734</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1517,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613468</v>
+        <v>613523</v>
       </c>
       <c r="R10" t="n">
-        <v>7041729</v>
+        <v>7041633</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1570,12 +1575,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,7 +1607,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121255009</v>
+        <v>121255010</v>
       </c>
       <c r="B11" t="n">
         <v>90720</v>
@@ -1642,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613396</v>
+        <v>613391</v>
       </c>
       <c r="R11" t="n">
-        <v>7041771</v>
+        <v>7041765</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1704,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121255054</v>
+        <v>121255006</v>
       </c>
       <c r="B12" t="n">
-        <v>98105</v>
+        <v>74715</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,42 +1721,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613568</v>
+        <v>613519</v>
       </c>
       <c r="R12" t="n">
-        <v>7041618</v>
+        <v>7041683</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1763,7 +1764,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1773,17 +1774,17 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1810,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121255025</v>
+        <v>121255058</v>
       </c>
       <c r="B13" t="n">
-        <v>91160</v>
+        <v>91376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1826,21 +1827,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1850,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613463</v>
+        <v>613546</v>
       </c>
       <c r="R13" t="n">
-        <v>7041737</v>
+        <v>7041646</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1880,12 +1881,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,7 +1913,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121255050</v>
+        <v>121255051</v>
       </c>
       <c r="B14" t="n">
         <v>79690</v>
@@ -1952,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613348</v>
+        <v>613451</v>
       </c>
       <c r="R14" t="n">
-        <v>7041806</v>
+        <v>7041510</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1996,7 +1997,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121255055</v>
+        <v>121255037</v>
       </c>
       <c r="B15" t="n">
-        <v>98105</v>
+        <v>90685</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,42 +2027,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613400</v>
+        <v>613554</v>
       </c>
       <c r="R15" t="n">
-        <v>7041781</v>
+        <v>7041628</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2223,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121255034</v>
+        <v>121255013</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2239,21 +2235,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2263,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613618</v>
+        <v>613465</v>
       </c>
       <c r="R17" t="n">
-        <v>7041721</v>
+        <v>7041678</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2278,7 +2274,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2288,7 +2284,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2325,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121255032</v>
+        <v>121255029</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,38 +2333,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613446</v>
+        <v>613510</v>
       </c>
       <c r="R18" t="n">
-        <v>7041752</v>
+        <v>7041675</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121255016</v>
+        <v>121255032</v>
       </c>
       <c r="B19" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613505</v>
+        <v>613446</v>
       </c>
       <c r="R19" t="n">
-        <v>7041675</v>
+        <v>7041752</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2529,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121255024</v>
+        <v>121255042</v>
       </c>
       <c r="B20" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2545,39 +2545,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613541</v>
+        <v>613460</v>
       </c>
       <c r="R20" t="n">
-        <v>7041685</v>
+        <v>7041672</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2604,12 +2599,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2636,10 +2631,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121255051</v>
+        <v>121255024</v>
       </c>
       <c r="B21" t="n">
-        <v>79690</v>
+        <v>57372</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2652,34 +2647,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613451</v>
+        <v>613541</v>
       </c>
       <c r="R21" t="n">
-        <v>7041510</v>
+        <v>7041685</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2738,7 +2738,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121255019</v>
+        <v>121255044</v>
       </c>
       <c r="B22" t="n">
         <v>57356</v>
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613528</v>
+        <v>613475</v>
       </c>
       <c r="R22" t="n">
-        <v>7041701</v>
+        <v>7041662</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2813,17 +2813,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2952,7 +2952,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121255053</v>
+        <v>121255052</v>
       </c>
       <c r="B24" t="n">
         <v>98105</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613554</v>
+        <v>613542</v>
       </c>
       <c r="R24" t="n">
-        <v>7041573</v>
+        <v>7041572</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3058,10 +3058,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121255040</v>
+        <v>121255050</v>
       </c>
       <c r="B25" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3074,21 +3074,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613542</v>
+        <v>613348</v>
       </c>
       <c r="R25" t="n">
-        <v>7041619</v>
+        <v>7041806</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3142,6 +3142,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3160,10 +3161,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121255008</v>
+        <v>121255054</v>
       </c>
       <c r="B26" t="n">
-        <v>90685</v>
+        <v>98105</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3172,38 +3173,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>613391</v>
+        <v>613568</v>
       </c>
       <c r="R26" t="n">
-        <v>7041765</v>
+        <v>7041618</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3215,7 +3220,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3225,17 +3230,17 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3262,7 +3267,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121255014</v>
+        <v>121255041</v>
       </c>
       <c r="B27" t="n">
         <v>90720</v>
@@ -3302,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>613462</v>
+        <v>613536</v>
       </c>
       <c r="R27" t="n">
-        <v>7041669</v>
+        <v>7041639</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3332,12 +3337,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3364,7 +3369,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121255052</v>
+        <v>121255055</v>
       </c>
       <c r="B28" t="n">
         <v>98105</v>
@@ -3399,7 +3404,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3408,10 +3413,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613542</v>
+        <v>613400</v>
       </c>
       <c r="R28" t="n">
-        <v>7041572</v>
+        <v>7041781</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3470,10 +3475,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121255010</v>
+        <v>121255049</v>
       </c>
       <c r="B29" t="n">
-        <v>90720</v>
+        <v>91160</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3482,25 +3487,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3510,10 +3515,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613391</v>
+        <v>613523</v>
       </c>
       <c r="R29" t="n">
-        <v>7041765</v>
+        <v>7041640</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3540,12 +3545,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3572,10 +3577,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121255038</v>
+        <v>121255056</v>
       </c>
       <c r="B30" t="n">
-        <v>90685</v>
+        <v>98105</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3584,38 +3589,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613396</v>
+        <v>613391</v>
       </c>
       <c r="R30" t="n">
-        <v>7041694</v>
+        <v>7041785</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3674,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121255039</v>
+        <v>121255048</v>
       </c>
       <c r="B31" t="n">
-        <v>90685</v>
+        <v>57372</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3686,38 +3695,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613386</v>
+        <v>613373</v>
       </c>
       <c r="R31" t="n">
-        <v>7041700</v>
+        <v>7041694</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3776,10 +3790,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121255012</v>
+        <v>121255025</v>
       </c>
       <c r="B32" t="n">
-        <v>90720</v>
+        <v>91160</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3788,25 +3802,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3816,10 +3830,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613454</v>
+        <v>613463</v>
       </c>
       <c r="R32" t="n">
-        <v>7041671</v>
+        <v>7041737</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3878,10 +3892,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121255043</v>
+        <v>121255038</v>
       </c>
       <c r="B33" t="n">
-        <v>90720</v>
+        <v>90685</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3890,25 +3904,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3918,10 +3932,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>613421</v>
+        <v>613396</v>
       </c>
       <c r="R33" t="n">
-        <v>7041692</v>
+        <v>7041694</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3980,7 +3994,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121255013</v>
+        <v>121255015</v>
       </c>
       <c r="B34" t="n">
         <v>90720</v>
@@ -4020,10 +4034,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>613465</v>
+        <v>613481</v>
       </c>
       <c r="R34" t="n">
-        <v>7041678</v>
+        <v>7041676</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4082,10 +4096,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121255044</v>
+        <v>121255046</v>
       </c>
       <c r="B35" t="n">
-        <v>57356</v>
+        <v>90740</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4098,39 +4112,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>613475</v>
+        <v>613534</v>
       </c>
       <c r="R35" t="n">
-        <v>7041662</v>
+        <v>7041558</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4163,11 +4172,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4194,10 +4198,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121255042</v>
+        <v>121255021</v>
       </c>
       <c r="B36" t="n">
-        <v>90720</v>
+        <v>79719</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4206,25 +4210,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4234,10 +4238,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613460</v>
+        <v>613468</v>
       </c>
       <c r="R36" t="n">
-        <v>7041672</v>
+        <v>7041729</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4264,12 +4268,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4296,10 +4300,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121255056</v>
+        <v>121255039</v>
       </c>
       <c r="B37" t="n">
-        <v>98105</v>
+        <v>90685</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4308,42 +4312,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613391</v>
+        <v>613386</v>
       </c>
       <c r="R37" t="n">
-        <v>7041785</v>
+        <v>7041700</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4402,7 +4402,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121255011</v>
+        <v>121255016</v>
       </c>
       <c r="B38" t="n">
         <v>90720</v>
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>613415</v>
+        <v>613505</v>
       </c>
       <c r="R38" t="n">
-        <v>7041708</v>
+        <v>7041675</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4504,10 +4504,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121255015</v>
+        <v>121255031</v>
       </c>
       <c r="B39" t="n">
-        <v>90720</v>
+        <v>90734</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4520,21 +4520,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>613481</v>
+        <v>613377</v>
       </c>
       <c r="R39" t="n">
-        <v>7041676</v>
+        <v>7041742</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4606,10 +4606,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121255037</v>
+        <v>121255023</v>
       </c>
       <c r="B40" t="n">
-        <v>90685</v>
+        <v>57372</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4618,38 +4618,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>613554</v>
+        <v>613442</v>
       </c>
       <c r="R40" t="n">
-        <v>7041628</v>
+        <v>7041756</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4676,12 +4681,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4708,10 +4713,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121255048</v>
+        <v>121255040</v>
       </c>
       <c r="B41" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4724,39 +4729,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>613373</v>
+        <v>613542</v>
       </c>
       <c r="R41" t="n">
-        <v>7041694</v>
+        <v>7041619</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4815,10 +4815,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121255058</v>
+        <v>121255012</v>
       </c>
       <c r="B42" t="n">
-        <v>91376</v>
+        <v>90720</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4827,25 +4827,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>613546</v>
+        <v>613454</v>
       </c>
       <c r="R42" t="n">
-        <v>7041646</v>
+        <v>7041671</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255053</v>
+        <v>121255039</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>90685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613554</v>
+        <v>613386</v>
       </c>
       <c r="R2" t="n">
-        <v>7041573</v>
+        <v>7041700</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255011</v>
+        <v>121255032</v>
       </c>
       <c r="B3" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613415</v>
+        <v>613446</v>
       </c>
       <c r="R3" t="n">
-        <v>7041708</v>
+        <v>7041752</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121255043</v>
+        <v>121255057</v>
       </c>
       <c r="B4" t="n">
-        <v>90720</v>
+        <v>90734</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613421</v>
+        <v>613523</v>
       </c>
       <c r="R4" t="n">
-        <v>7041692</v>
+        <v>7041633</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121255008</v>
+        <v>121255019</v>
       </c>
       <c r="B5" t="n">
-        <v>90685</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,38 +993,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613391</v>
+        <v>613528</v>
       </c>
       <c r="R5" t="n">
-        <v>7041765</v>
+        <v>7041701</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1061,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121255009</v>
+        <v>121255024</v>
       </c>
       <c r="B6" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,34 +1109,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613396</v>
+        <v>613541</v>
       </c>
       <c r="R6" t="n">
-        <v>7041771</v>
+        <v>7041685</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1189,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121255019</v>
+        <v>121255011</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,39 +1216,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613528</v>
+        <v>613415</v>
       </c>
       <c r="R7" t="n">
-        <v>7041701</v>
+        <v>7041708</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1270,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121255034</v>
+        <v>121255021</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>79719</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,25 +1314,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613618</v>
+        <v>613468</v>
       </c>
       <c r="R8" t="n">
-        <v>7041721</v>
+        <v>7041729</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1356,7 +1357,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1366,7 +1367,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1403,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121255014</v>
+        <v>121255012</v>
       </c>
       <c r="B9" t="n">
         <v>90720</v>
@@ -1443,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613462</v>
+        <v>613454</v>
       </c>
       <c r="R9" t="n">
-        <v>7041669</v>
+        <v>7041671</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121255057</v>
+        <v>121255050</v>
       </c>
       <c r="B10" t="n">
-        <v>90734</v>
+        <v>79690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613523</v>
+        <v>613348</v>
       </c>
       <c r="R10" t="n">
-        <v>7041633</v>
+        <v>7041806</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1589,6 +1590,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1607,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121255010</v>
+        <v>121255045</v>
       </c>
       <c r="B11" t="n">
-        <v>90720</v>
+        <v>56568</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,25 +1621,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613391</v>
+        <v>613481</v>
       </c>
       <c r="R11" t="n">
-        <v>7041765</v>
+        <v>7041555</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1677,12 +1679,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1709,10 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121255006</v>
+        <v>121255054</v>
       </c>
       <c r="B12" t="n">
-        <v>74715</v>
+        <v>98105</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,38 +1723,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613519</v>
+        <v>613568</v>
       </c>
       <c r="R12" t="n">
-        <v>7041683</v>
+        <v>7041618</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1764,7 +1770,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1774,17 +1780,17 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1811,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121255058</v>
+        <v>121255034</v>
       </c>
       <c r="B13" t="n">
-        <v>91376</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613546</v>
+        <v>613618</v>
       </c>
       <c r="R13" t="n">
-        <v>7041646</v>
+        <v>7041721</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1866,7 +1872,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1876,17 +1882,17 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1913,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121255051</v>
+        <v>121255044</v>
       </c>
       <c r="B14" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,34 +1935,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613451</v>
+        <v>613475</v>
       </c>
       <c r="R14" t="n">
-        <v>7041510</v>
+        <v>7041662</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1989,6 +2000,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2015,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121255037</v>
+        <v>121255053</v>
       </c>
       <c r="B15" t="n">
-        <v>90685</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,28 +2043,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
@@ -2058,7 +2078,7 @@
         <v>613554</v>
       </c>
       <c r="R15" t="n">
-        <v>7041628</v>
+        <v>7041573</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2219,10 +2239,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121255013</v>
+        <v>121255031</v>
       </c>
       <c r="B17" t="n">
-        <v>90720</v>
+        <v>90734</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,21 +2255,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2279,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613465</v>
+        <v>613377</v>
       </c>
       <c r="R17" t="n">
-        <v>7041678</v>
+        <v>7041742</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2321,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121255029</v>
+        <v>121255051</v>
       </c>
       <c r="B18" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,42 +2353,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613510</v>
+        <v>613451</v>
       </c>
       <c r="R18" t="n">
-        <v>7041675</v>
+        <v>7041510</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2395,12 +2411,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2427,10 +2443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121255032</v>
+        <v>121255008</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>90685</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,25 +2455,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2467,10 +2483,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613446</v>
+        <v>613391</v>
       </c>
       <c r="R19" t="n">
-        <v>7041752</v>
+        <v>7041765</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2529,7 +2545,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121255042</v>
+        <v>121255013</v>
       </c>
       <c r="B20" t="n">
         <v>90720</v>
@@ -2569,10 +2585,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613460</v>
+        <v>613465</v>
       </c>
       <c r="R20" t="n">
-        <v>7041672</v>
+        <v>7041678</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2599,12 +2615,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2631,10 +2647,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121255024</v>
+        <v>121255015</v>
       </c>
       <c r="B21" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2647,39 +2663,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613541</v>
+        <v>613481</v>
       </c>
       <c r="R21" t="n">
-        <v>7041685</v>
+        <v>7041676</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2738,10 +2749,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121255044</v>
+        <v>121255046</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>90740</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2754,39 +2765,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613475</v>
+        <v>613534</v>
       </c>
       <c r="R22" t="n">
-        <v>7041662</v>
+        <v>7041558</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2819,11 +2825,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2850,10 +2851,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121255045</v>
+        <v>121255006</v>
       </c>
       <c r="B23" t="n">
-        <v>56568</v>
+        <v>74715</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,25 +2863,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2890,10 +2891,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613481</v>
+        <v>613519</v>
       </c>
       <c r="R23" t="n">
-        <v>7041555</v>
+        <v>7041683</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2920,12 +2921,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2952,10 +2953,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121255052</v>
+        <v>121255043</v>
       </c>
       <c r="B24" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2964,42 +2965,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613542</v>
+        <v>613421</v>
       </c>
       <c r="R24" t="n">
-        <v>7041572</v>
+        <v>7041692</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3058,10 +3055,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121255050</v>
+        <v>121255010</v>
       </c>
       <c r="B25" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3074,21 +3071,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3098,10 +3095,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613348</v>
+        <v>613391</v>
       </c>
       <c r="R25" t="n">
-        <v>7041806</v>
+        <v>7041765</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3128,12 +3125,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3142,7 +3139,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3161,10 +3157,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121255054</v>
+        <v>121255025</v>
       </c>
       <c r="B26" t="n">
-        <v>98105</v>
+        <v>91160</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3177,38 +3173,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>613568</v>
+        <v>613463</v>
       </c>
       <c r="R26" t="n">
-        <v>7041618</v>
+        <v>7041737</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3220,7 +3212,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3230,17 +3222,17 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3369,10 +3361,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121255055</v>
+        <v>121255058</v>
       </c>
       <c r="B28" t="n">
-        <v>98105</v>
+        <v>91376</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3385,38 +3377,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613400</v>
+        <v>613546</v>
       </c>
       <c r="R28" t="n">
-        <v>7041781</v>
+        <v>7041646</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3475,10 +3463,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121255049</v>
+        <v>121255055</v>
       </c>
       <c r="B29" t="n">
-        <v>91160</v>
+        <v>98105</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3491,34 +3479,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613523</v>
+        <v>613400</v>
       </c>
       <c r="R29" t="n">
-        <v>7041640</v>
+        <v>7041781</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3577,10 +3569,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121255056</v>
+        <v>121255042</v>
       </c>
       <c r="B30" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3589,42 +3581,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613391</v>
+        <v>613460</v>
       </c>
       <c r="R30" t="n">
-        <v>7041785</v>
+        <v>7041672</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3683,10 +3671,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121255048</v>
+        <v>121255037</v>
       </c>
       <c r="B31" t="n">
-        <v>57372</v>
+        <v>90685</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3695,43 +3683,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613373</v>
+        <v>613554</v>
       </c>
       <c r="R31" t="n">
-        <v>7041694</v>
+        <v>7041628</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3790,10 +3773,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121255025</v>
+        <v>121255056</v>
       </c>
       <c r="B32" t="n">
-        <v>91160</v>
+        <v>98105</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3806,34 +3789,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613463</v>
+        <v>613391</v>
       </c>
       <c r="R32" t="n">
-        <v>7041737</v>
+        <v>7041785</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3860,12 +3847,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3892,10 +3879,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121255038</v>
+        <v>121255023</v>
       </c>
       <c r="B33" t="n">
-        <v>90685</v>
+        <v>57372</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3904,38 +3891,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>613396</v>
+        <v>613442</v>
       </c>
       <c r="R33" t="n">
-        <v>7041694</v>
+        <v>7041756</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3962,12 +3954,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3994,10 +3986,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121255015</v>
+        <v>121255029</v>
       </c>
       <c r="B34" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4006,38 +3998,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>613481</v>
+        <v>613510</v>
       </c>
       <c r="R34" t="n">
-        <v>7041676</v>
+        <v>7041675</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4096,10 +4092,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121255046</v>
+        <v>121255040</v>
       </c>
       <c r="B35" t="n">
-        <v>90740</v>
+        <v>90720</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4112,21 +4108,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4136,10 +4132,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>613534</v>
+        <v>613542</v>
       </c>
       <c r="R35" t="n">
-        <v>7041558</v>
+        <v>7041619</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4198,10 +4194,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121255021</v>
+        <v>121255052</v>
       </c>
       <c r="B36" t="n">
-        <v>79719</v>
+        <v>98105</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4210,38 +4206,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613468</v>
+        <v>613542</v>
       </c>
       <c r="R36" t="n">
-        <v>7041729</v>
+        <v>7041572</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4300,10 +4300,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121255039</v>
+        <v>121255016</v>
       </c>
       <c r="B37" t="n">
-        <v>90685</v>
+        <v>90720</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4312,25 +4312,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613386</v>
+        <v>613505</v>
       </c>
       <c r="R37" t="n">
-        <v>7041700</v>
+        <v>7041675</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4402,10 +4402,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121255016</v>
+        <v>121255038</v>
       </c>
       <c r="B38" t="n">
-        <v>90720</v>
+        <v>90685</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4414,25 +4414,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>613505</v>
+        <v>613396</v>
       </c>
       <c r="R38" t="n">
-        <v>7041675</v>
+        <v>7041694</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4472,12 +4472,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4504,10 +4504,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121255031</v>
+        <v>121255049</v>
       </c>
       <c r="B39" t="n">
-        <v>90734</v>
+        <v>91160</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4516,25 +4516,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>613377</v>
+        <v>613523</v>
       </c>
       <c r="R39" t="n">
-        <v>7041742</v>
+        <v>7041640</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4606,10 +4606,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121255023</v>
+        <v>121255014</v>
       </c>
       <c r="B40" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4622,39 +4622,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>613442</v>
+        <v>613462</v>
       </c>
       <c r="R40" t="n">
-        <v>7041756</v>
+        <v>7041669</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4713,7 +4708,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121255040</v>
+        <v>121255009</v>
       </c>
       <c r="B41" t="n">
         <v>90720</v>
@@ -4753,10 +4748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>613542</v>
+        <v>613396</v>
       </c>
       <c r="R41" t="n">
-        <v>7041619</v>
+        <v>7041771</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4783,12 +4778,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4815,10 +4810,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121255012</v>
+        <v>121255048</v>
       </c>
       <c r="B42" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4831,34 +4826,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>613454</v>
+        <v>613373</v>
       </c>
       <c r="R42" t="n">
-        <v>7041671</v>
+        <v>7041694</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255039</v>
+        <v>121255050</v>
       </c>
       <c r="B2" t="n">
-        <v>90685</v>
+        <v>79690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613386</v>
+        <v>613348</v>
       </c>
       <c r="R2" t="n">
-        <v>7041700</v>
+        <v>7041806</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -759,6 +759,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255032</v>
+        <v>121255021</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>79719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +790,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613446</v>
+        <v>613468</v>
       </c>
       <c r="R3" t="n">
-        <v>7041752</v>
+        <v>7041729</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121255057</v>
+        <v>121255044</v>
       </c>
       <c r="B4" t="n">
-        <v>90734</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +896,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613523</v>
+        <v>613475</v>
       </c>
       <c r="R4" t="n">
-        <v>7041633</v>
+        <v>7041662</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -955,6 +961,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121255019</v>
+        <v>121255011</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,39 +1008,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613528</v>
+        <v>613415</v>
       </c>
       <c r="R5" t="n">
-        <v>7041701</v>
+        <v>7041708</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1062,11 +1068,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121255024</v>
+        <v>121255046</v>
       </c>
       <c r="B6" t="n">
-        <v>57372</v>
+        <v>90740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,39 +1110,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613541</v>
+        <v>613534</v>
       </c>
       <c r="R6" t="n">
-        <v>7041685</v>
+        <v>7041558</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1168,12 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121255011</v>
+        <v>121255024</v>
       </c>
       <c r="B7" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,34 +1212,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613415</v>
+        <v>613541</v>
       </c>
       <c r="R7" t="n">
-        <v>7041708</v>
+        <v>7041685</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1302,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121255021</v>
+        <v>121255012</v>
       </c>
       <c r="B8" t="n">
-        <v>79719</v>
+        <v>90720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,25 +1315,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613468</v>
+        <v>613454</v>
       </c>
       <c r="R8" t="n">
-        <v>7041729</v>
+        <v>7041671</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1404,7 +1405,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121255012</v>
+        <v>121255015</v>
       </c>
       <c r="B9" t="n">
         <v>90720</v>
@@ -1444,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613454</v>
+        <v>613481</v>
       </c>
       <c r="R9" t="n">
-        <v>7041671</v>
+        <v>7041676</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1506,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121255050</v>
+        <v>121255048</v>
       </c>
       <c r="B10" t="n">
-        <v>79690</v>
+        <v>57372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,34 +1523,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613348</v>
+        <v>613373</v>
       </c>
       <c r="R10" t="n">
-        <v>7041806</v>
+        <v>7041694</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1590,7 +1596,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1609,10 +1614,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121255045</v>
+        <v>121255054</v>
       </c>
       <c r="B11" t="n">
-        <v>56568</v>
+        <v>98105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1621,38 +1626,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613481</v>
+        <v>613568</v>
       </c>
       <c r="R11" t="n">
-        <v>7041555</v>
+        <v>7041618</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1664,7 +1673,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1674,7 +1683,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1711,7 +1720,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121255054</v>
+        <v>121255029</v>
       </c>
       <c r="B12" t="n">
         <v>98105</v>
@@ -1746,7 +1755,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1755,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613568</v>
+        <v>613510</v>
       </c>
       <c r="R12" t="n">
-        <v>7041618</v>
+        <v>7041675</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1770,7 +1779,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1780,17 +1789,17 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121255034</v>
+        <v>121255052</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,38 +1838,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613618</v>
+        <v>613542</v>
       </c>
       <c r="R13" t="n">
-        <v>7041721</v>
+        <v>7041572</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1872,7 +1885,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1882,17 +1895,17 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,10 +1932,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121255044</v>
+        <v>121255042</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,39 +1948,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613475</v>
+        <v>613460</v>
       </c>
       <c r="R14" t="n">
-        <v>7041662</v>
+        <v>7041672</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2000,11 +2008,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,10 +2034,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121255053</v>
+        <v>121255037</v>
       </c>
       <c r="B15" t="n">
-        <v>98105</v>
+        <v>90685</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2043,32 +2046,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
@@ -2078,7 +2077,7 @@
         <v>613554</v>
       </c>
       <c r="R15" t="n">
-        <v>7041573</v>
+        <v>7041628</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2239,10 +2238,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121255031</v>
+        <v>121255032</v>
       </c>
       <c r="B17" t="n">
-        <v>90734</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2255,21 +2254,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2279,10 +2278,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613377</v>
+        <v>613446</v>
       </c>
       <c r="R17" t="n">
-        <v>7041742</v>
+        <v>7041752</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2341,10 +2340,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121255051</v>
+        <v>121255045</v>
       </c>
       <c r="B18" t="n">
-        <v>79690</v>
+        <v>56568</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,25 +2352,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2381,10 +2380,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613451</v>
+        <v>613481</v>
       </c>
       <c r="R18" t="n">
-        <v>7041510</v>
+        <v>7041555</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2443,10 +2442,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121255008</v>
+        <v>121255009</v>
       </c>
       <c r="B19" t="n">
-        <v>90685</v>
+        <v>90720</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,25 +2454,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2483,10 +2482,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613391</v>
+        <v>613396</v>
       </c>
       <c r="R19" t="n">
-        <v>7041765</v>
+        <v>7041771</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2545,10 +2544,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121255013</v>
+        <v>121255038</v>
       </c>
       <c r="B20" t="n">
-        <v>90720</v>
+        <v>90685</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,25 +2556,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2585,10 +2584,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613465</v>
+        <v>613396</v>
       </c>
       <c r="R20" t="n">
-        <v>7041678</v>
+        <v>7041694</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2615,12 +2614,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2647,10 +2646,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121255015</v>
+        <v>121255039</v>
       </c>
       <c r="B21" t="n">
-        <v>90720</v>
+        <v>90685</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2659,25 +2658,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2687,10 +2686,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613481</v>
+        <v>613386</v>
       </c>
       <c r="R21" t="n">
-        <v>7041676</v>
+        <v>7041700</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2717,12 +2716,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2749,10 +2748,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121255046</v>
+        <v>121255006</v>
       </c>
       <c r="B22" t="n">
-        <v>90740</v>
+        <v>74715</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2765,21 +2764,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2789,10 +2788,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613534</v>
+        <v>613519</v>
       </c>
       <c r="R22" t="n">
-        <v>7041558</v>
+        <v>7041683</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2819,12 +2818,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2851,10 +2850,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121255006</v>
+        <v>121255019</v>
       </c>
       <c r="B23" t="n">
-        <v>74715</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2867,34 +2866,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613519</v>
+        <v>613528</v>
       </c>
       <c r="R23" t="n">
-        <v>7041683</v>
+        <v>7041701</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2927,6 +2931,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2953,7 +2962,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121255043</v>
+        <v>121255041</v>
       </c>
       <c r="B24" t="n">
         <v>90720</v>
@@ -2993,10 +3002,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613421</v>
+        <v>613536</v>
       </c>
       <c r="R24" t="n">
-        <v>7041692</v>
+        <v>7041639</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3055,10 +3064,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121255010</v>
+        <v>121255025</v>
       </c>
       <c r="B25" t="n">
-        <v>90720</v>
+        <v>91160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3067,25 +3076,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3095,10 +3104,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613391</v>
+        <v>613463</v>
       </c>
       <c r="R25" t="n">
-        <v>7041765</v>
+        <v>7041737</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3157,10 +3166,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121255025</v>
+        <v>121255056</v>
       </c>
       <c r="B26" t="n">
-        <v>91160</v>
+        <v>98105</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3173,34 +3182,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>613463</v>
+        <v>613391</v>
       </c>
       <c r="R26" t="n">
-        <v>7041737</v>
+        <v>7041785</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3227,12 +3240,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3259,7 +3272,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121255041</v>
+        <v>121255016</v>
       </c>
       <c r="B27" t="n">
         <v>90720</v>
@@ -3299,10 +3312,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>613536</v>
+        <v>613505</v>
       </c>
       <c r="R27" t="n">
-        <v>7041639</v>
+        <v>7041675</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3329,12 +3342,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3463,10 +3476,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121255055</v>
+        <v>121255034</v>
       </c>
       <c r="B29" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3475,42 +3488,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613400</v>
+        <v>613618</v>
       </c>
       <c r="R29" t="n">
-        <v>7041781</v>
+        <v>7041721</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3522,7 +3531,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3532,17 +3541,17 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3569,10 +3578,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121255042</v>
+        <v>121255053</v>
       </c>
       <c r="B30" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3581,38 +3590,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613460</v>
+        <v>613554</v>
       </c>
       <c r="R30" t="n">
-        <v>7041672</v>
+        <v>7041573</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3671,10 +3684,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121255037</v>
+        <v>121255043</v>
       </c>
       <c r="B31" t="n">
-        <v>90685</v>
+        <v>90720</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3683,25 +3696,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3711,10 +3724,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613554</v>
+        <v>613421</v>
       </c>
       <c r="R31" t="n">
-        <v>7041628</v>
+        <v>7041692</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3773,10 +3786,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121255056</v>
+        <v>121255031</v>
       </c>
       <c r="B32" t="n">
-        <v>98105</v>
+        <v>90734</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3785,42 +3798,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613391</v>
+        <v>613377</v>
       </c>
       <c r="R32" t="n">
-        <v>7041785</v>
+        <v>7041742</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3847,12 +3856,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3879,10 +3888,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121255023</v>
+        <v>121255014</v>
       </c>
       <c r="B33" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3895,39 +3904,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>613442</v>
+        <v>613462</v>
       </c>
       <c r="R33" t="n">
-        <v>7041756</v>
+        <v>7041669</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3986,10 +3990,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121255029</v>
+        <v>121255057</v>
       </c>
       <c r="B34" t="n">
-        <v>98105</v>
+        <v>90734</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3998,42 +4002,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>613510</v>
+        <v>613523</v>
       </c>
       <c r="R34" t="n">
-        <v>7041675</v>
+        <v>7041633</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4060,12 +4060,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4092,7 +4092,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121255040</v>
+        <v>121255010</v>
       </c>
       <c r="B35" t="n">
         <v>90720</v>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>613542</v>
+        <v>613391</v>
       </c>
       <c r="R35" t="n">
-        <v>7041619</v>
+        <v>7041765</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4162,12 +4162,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4194,10 +4194,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121255052</v>
+        <v>121255008</v>
       </c>
       <c r="B36" t="n">
-        <v>98105</v>
+        <v>90685</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4206,42 +4206,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613542</v>
+        <v>613391</v>
       </c>
       <c r="R36" t="n">
-        <v>7041572</v>
+        <v>7041765</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4268,12 +4264,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4300,10 +4296,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121255016</v>
+        <v>121255049</v>
       </c>
       <c r="B37" t="n">
-        <v>90720</v>
+        <v>91160</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4312,25 +4308,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4340,10 +4336,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613505</v>
+        <v>613523</v>
       </c>
       <c r="R37" t="n">
-        <v>7041675</v>
+        <v>7041640</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4370,12 +4366,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4402,10 +4398,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121255038</v>
+        <v>121255023</v>
       </c>
       <c r="B38" t="n">
-        <v>90685</v>
+        <v>57372</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4414,38 +4410,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>613396</v>
+        <v>613442</v>
       </c>
       <c r="R38" t="n">
-        <v>7041694</v>
+        <v>7041756</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4472,12 +4473,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4504,10 +4505,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121255049</v>
+        <v>121255055</v>
       </c>
       <c r="B39" t="n">
-        <v>91160</v>
+        <v>98105</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4520,34 +4521,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>613523</v>
+        <v>613400</v>
       </c>
       <c r="R39" t="n">
-        <v>7041640</v>
+        <v>7041781</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4606,7 +4611,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121255014</v>
+        <v>121255013</v>
       </c>
       <c r="B40" t="n">
         <v>90720</v>
@@ -4646,10 +4651,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>613462</v>
+        <v>613465</v>
       </c>
       <c r="R40" t="n">
-        <v>7041669</v>
+        <v>7041678</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4708,7 +4713,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121255009</v>
+        <v>121255040</v>
       </c>
       <c r="B41" t="n">
         <v>90720</v>
@@ -4748,10 +4753,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>613396</v>
+        <v>613542</v>
       </c>
       <c r="R41" t="n">
-        <v>7041771</v>
+        <v>7041619</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4778,12 +4783,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4810,10 +4815,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121255048</v>
+        <v>121255051</v>
       </c>
       <c r="B42" t="n">
-        <v>57372</v>
+        <v>79690</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4826,39 +4831,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>613373</v>
+        <v>613451</v>
       </c>
       <c r="R42" t="n">
-        <v>7041694</v>
+        <v>7041510</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 32459-2024 artfynd.xlsx
+++ b/artfynd/A 32459-2024 artfynd.xlsx
@@ -1094,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121255046</v>
+        <v>121255024</v>
       </c>
       <c r="B6" t="n">
-        <v>90740</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,34 +1110,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613534</v>
+        <v>613541</v>
       </c>
       <c r="R6" t="n">
-        <v>7041558</v>
+        <v>7041685</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1164,12 +1169,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121255024</v>
+        <v>121255046</v>
       </c>
       <c r="B7" t="n">
-        <v>57372</v>
+        <v>90740</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,39 +1217,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613541</v>
+        <v>613534</v>
       </c>
       <c r="R7" t="n">
-        <v>7041685</v>
+        <v>7041558</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -3476,10 +3476,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121255034</v>
+        <v>121255053</v>
       </c>
       <c r="B29" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3488,38 +3488,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613618</v>
+        <v>613554</v>
       </c>
       <c r="R29" t="n">
-        <v>7041721</v>
+        <v>7041573</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3531,7 +3535,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>Örnsköldsvik</t>
+          <t>Sollefteå</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3541,17 +3545,17 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Anundsjö</t>
+          <t>Resele</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3578,10 +3582,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121255053</v>
+        <v>121255034</v>
       </c>
       <c r="B30" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3590,42 +3594,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stugusjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613554</v>
+        <v>613618</v>
       </c>
       <c r="R30" t="n">
-        <v>7041573</v>
+        <v>7041721</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Sollefteå</t>
+          <t>Örnsköldsvik</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Resele</t>
+          <t>Anundsjö</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
